--- a/synthetic/output/payouts/payouts.xlsx
+++ b/synthetic/output/payouts/payouts.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H197"/>
+  <dimension ref="A1:H260"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -469,7 +469,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>P010</t>
+          <t>P029</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -478,10 +478,10 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>3619</v>
+        <v>0</v>
       </c>
       <c r="F2" t="n">
-        <v>3619</v>
+        <v>0</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
@@ -503,7 +503,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>P010</t>
+          <t>P029</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -512,10 +512,10 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>3822.02</v>
+        <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>3822.02</v>
+        <v>0</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
@@ -537,7 +537,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>P010</t>
+          <t>P029</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -546,10 +546,10 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4163.48</v>
+        <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>4163.48</v>
+        <v>0</v>
       </c>
       <c r="G4" t="n">
         <v>0</v>
@@ -571,7 +571,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>P010</t>
+          <t>P029</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -580,10 +580,10 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4091.31</v>
+        <v>0</v>
       </c>
       <c r="F5" t="n">
-        <v>4091.31</v>
+        <v>0</v>
       </c>
       <c r="G5" t="n">
         <v>0</v>
@@ -605,7 +605,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>P010</t>
+          <t>P029</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -614,10 +614,10 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>3804.01</v>
+        <v>506.34</v>
       </c>
       <c r="F6" t="n">
-        <v>3804.01</v>
+        <v>506.34</v>
       </c>
       <c r="G6" t="n">
         <v>0</v>
@@ -639,7 +639,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>P010</t>
+          <t>P029</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -648,10 +648,10 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>3857.05</v>
+        <v>0</v>
       </c>
       <c r="F7" t="n">
-        <v>3857.05</v>
+        <v>0</v>
       </c>
       <c r="G7" t="n">
         <v>0</v>
@@ -673,7 +673,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>P010</t>
+          <t>P029</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -682,10 +682,10 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>3973.46</v>
+        <v>0</v>
       </c>
       <c r="F8" t="n">
-        <v>3973.46</v>
+        <v>0</v>
       </c>
       <c r="G8" t="n">
         <v>0</v>
@@ -707,7 +707,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>P014</t>
+          <t>P027</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -716,10 +716,10 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>3801.94</v>
+        <v>5361.68</v>
       </c>
       <c r="F9" t="n">
-        <v>3801.94</v>
+        <v>5361.68</v>
       </c>
       <c r="G9" t="n">
         <v>0</v>
@@ -741,7 +741,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>P014</t>
+          <t>P027</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -750,10 +750,10 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>0</v>
+        <v>4522.88</v>
       </c>
       <c r="F10" t="n">
-        <v>0</v>
+        <v>4522.88</v>
       </c>
       <c r="G10" t="n">
         <v>0</v>
@@ -775,7 +775,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>P014</t>
+          <t>P027</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -784,10 +784,10 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>0</v>
+        <v>5297.34</v>
       </c>
       <c r="F11" t="n">
-        <v>0</v>
+        <v>5297.34</v>
       </c>
       <c r="G11" t="n">
         <v>0</v>
@@ -809,7 +809,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>P014</t>
+          <t>P027</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -818,10 +818,10 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>0</v>
+        <v>5205.17</v>
       </c>
       <c r="F12" t="n">
-        <v>0</v>
+        <v>5205.17</v>
       </c>
       <c r="G12" t="n">
         <v>0</v>
@@ -843,7 +843,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>P014</t>
+          <t>P027</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -852,10 +852,10 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>130.68</v>
+        <v>5235.41</v>
       </c>
       <c r="F13" t="n">
-        <v>130.68</v>
+        <v>5235.41</v>
       </c>
       <c r="G13" t="n">
         <v>0</v>
@@ -877,7 +877,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>P014</t>
+          <t>P027</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -886,10 +886,10 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>0</v>
+        <v>5150.28</v>
       </c>
       <c r="F14" t="n">
-        <v>0</v>
+        <v>5150.28</v>
       </c>
       <c r="G14" t="n">
         <v>0</v>
@@ -911,7 +911,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>P014</t>
+          <t>P027</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -920,10 +920,10 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>0</v>
+        <v>5345.35</v>
       </c>
       <c r="F15" t="n">
-        <v>0</v>
+        <v>5345.35</v>
       </c>
       <c r="G15" t="n">
         <v>0</v>
@@ -945,7 +945,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>P006</t>
+          <t>P026</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -954,10 +954,10 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>3555.09</v>
+        <v>2548.23</v>
       </c>
       <c r="F16" t="n">
-        <v>3555.09</v>
+        <v>2548.23</v>
       </c>
       <c r="G16" t="n">
         <v>0</v>
@@ -979,7 +979,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>P006</t>
+          <t>P026</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -988,10 +988,10 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>3859.08</v>
+        <v>2456.74</v>
       </c>
       <c r="F17" t="n">
-        <v>3859.08</v>
+        <v>2456.74</v>
       </c>
       <c r="G17" t="n">
         <v>0</v>
@@ -1013,7 +1013,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>P006</t>
+          <t>P026</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -1022,13 +1022,13 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>4004.37</v>
+        <v>2150.95</v>
       </c>
       <c r="F18" t="n">
-        <v>4004.37</v>
+        <v>7192.55</v>
       </c>
       <c r="G18" t="n">
-        <v>0</v>
+        <v>5041.6</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
@@ -1047,7 +1047,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>P006</t>
+          <t>P026</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -1056,10 +1056,10 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>5787.19</v>
+        <v>2263.33</v>
       </c>
       <c r="F19" t="n">
-        <v>5787.19</v>
+        <v>2263.33</v>
       </c>
       <c r="G19" t="n">
         <v>0</v>
@@ -1081,7 +1081,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>P006</t>
+          <t>P026</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -1090,10 +1090,10 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>3688.56</v>
+        <v>2622.14</v>
       </c>
       <c r="F20" t="n">
-        <v>3688.56</v>
+        <v>2622.14</v>
       </c>
       <c r="G20" t="n">
         <v>0</v>
@@ -1115,7 +1115,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>P006</t>
+          <t>P026</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -1124,10 +1124,10 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>3651.45</v>
+        <v>2561.92</v>
       </c>
       <c r="F21" t="n">
-        <v>3651.45</v>
+        <v>2561.92</v>
       </c>
       <c r="G21" t="n">
         <v>0</v>
@@ -1149,7 +1149,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>P006</t>
+          <t>P026</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -1158,10 +1158,10 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>3769.3</v>
+        <v>2423.99</v>
       </c>
       <c r="F22" t="n">
-        <v>3769.3</v>
+        <v>2423.99</v>
       </c>
       <c r="G22" t="n">
         <v>0</v>
@@ -1178,12 +1178,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>FR0002</t>
+          <t>FR0001</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>P019</t>
+          <t>P010</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -1192,13 +1192,13 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>0</v>
+        <v>3324.08</v>
       </c>
       <c r="F23" t="n">
-        <v>8548.07</v>
+        <v>3324.08</v>
       </c>
       <c r="G23" t="n">
-        <v>8548.07</v>
+        <v>0</v>
       </c>
       <c r="H23" t="inlineStr">
         <is>
@@ -1212,12 +1212,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>FR0002</t>
+          <t>FR0001</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>P019</t>
+          <t>P010</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -1226,10 +1226,10 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>0</v>
+        <v>3135.95</v>
       </c>
       <c r="F24" t="n">
-        <v>0</v>
+        <v>3135.95</v>
       </c>
       <c r="G24" t="n">
         <v>0</v>
@@ -1246,12 +1246,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>FR0002</t>
+          <t>FR0001</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>P019</t>
+          <t>P010</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -1260,10 +1260,10 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>0</v>
+        <v>2791.32</v>
       </c>
       <c r="F25" t="n">
-        <v>0</v>
+        <v>2791.32</v>
       </c>
       <c r="G25" t="n">
         <v>0</v>
@@ -1280,12 +1280,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>FR0002</t>
+          <t>FR0001</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>P019</t>
+          <t>P010</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -1294,10 +1294,10 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>0</v>
+        <v>2601.88</v>
       </c>
       <c r="F26" t="n">
-        <v>0</v>
+        <v>2601.88</v>
       </c>
       <c r="G26" t="n">
         <v>0</v>
@@ -1314,12 +1314,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>FR0002</t>
+          <t>FR0001</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>P019</t>
+          <t>P010</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -1328,10 +1328,10 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>0</v>
+        <v>3402.52</v>
       </c>
       <c r="F27" t="n">
-        <v>0</v>
+        <v>3402.52</v>
       </c>
       <c r="G27" t="n">
         <v>0</v>
@@ -1348,12 +1348,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>FR0002</t>
+          <t>FR0001</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>P019</t>
+          <t>P010</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -1362,10 +1362,10 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>0</v>
+        <v>2468.43</v>
       </c>
       <c r="F28" t="n">
-        <v>0</v>
+        <v>2468.43</v>
       </c>
       <c r="G28" t="n">
         <v>0</v>
@@ -1382,12 +1382,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>FR0002</t>
+          <t>FR0001</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>P019</t>
+          <t>P010</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -1396,10 +1396,10 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>0</v>
+        <v>2541.08</v>
       </c>
       <c r="F29" t="n">
-        <v>0</v>
+        <v>2541.08</v>
       </c>
       <c r="G29" t="n">
         <v>0</v>
@@ -1416,12 +1416,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>FR0002</t>
+          <t>FR0001</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>P004</t>
+          <t>P008</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -1430,10 +1430,10 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>4255.38</v>
+        <v>6484.06</v>
       </c>
       <c r="F30" t="n">
-        <v>4255.38</v>
+        <v>6484.06</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
@@ -1450,12 +1450,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>FR0002</t>
+          <t>FR0001</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>P004</t>
+          <t>P008</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -1464,10 +1464,10 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>4761.83</v>
+        <v>8340.049999999999</v>
       </c>
       <c r="F31" t="n">
-        <v>4761.83</v>
+        <v>8340.049999999999</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
@@ -1484,12 +1484,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>FR0002</t>
+          <t>FR0001</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>P004</t>
+          <t>P008</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -1498,10 +1498,10 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>4121.6</v>
+        <v>6372.07</v>
       </c>
       <c r="F32" t="n">
-        <v>4121.6</v>
+        <v>6372.07</v>
       </c>
       <c r="G32" t="n">
         <v>0</v>
@@ -1518,12 +1518,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>FR0002</t>
+          <t>FR0001</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>P004</t>
+          <t>P008</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -1532,10 +1532,10 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>4861.83</v>
+        <v>6954.37</v>
       </c>
       <c r="F33" t="n">
-        <v>4861.83</v>
+        <v>6954.37</v>
       </c>
       <c r="G33" t="n">
         <v>0</v>
@@ -1552,12 +1552,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>FR0002</t>
+          <t>FR0001</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>P004</t>
+          <t>P008</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -1566,10 +1566,10 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>4427.82</v>
+        <v>6902.8</v>
       </c>
       <c r="F34" t="n">
-        <v>4427.82</v>
+        <v>6902.8</v>
       </c>
       <c r="G34" t="n">
         <v>0</v>
@@ -1586,12 +1586,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>FR0002</t>
+          <t>FR0001</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>P004</t>
+          <t>P008</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -1600,10 +1600,10 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>4711.72</v>
+        <v>8476.639999999999</v>
       </c>
       <c r="F35" t="n">
-        <v>4711.72</v>
+        <v>8476.639999999999</v>
       </c>
       <c r="G35" t="n">
         <v>0</v>
@@ -1620,12 +1620,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>FR0002</t>
+          <t>FR0001</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>P004</t>
+          <t>P008</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -1634,10 +1634,10 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>4751.65</v>
+        <v>8482.42</v>
       </c>
       <c r="F36" t="n">
-        <v>4751.65</v>
+        <v>8482.42</v>
       </c>
       <c r="G36" t="n">
         <v>0</v>
@@ -1659,7 +1659,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>P003</t>
+          <t>P014</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -1668,13 +1668,13 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>285.74</v>
+        <v>1893.55</v>
       </c>
       <c r="F37" t="n">
-        <v>285.74</v>
+        <v>8274.959999999999</v>
       </c>
       <c r="G37" t="n">
-        <v>0</v>
+        <v>6381.4</v>
       </c>
       <c r="H37" t="inlineStr">
         <is>
@@ -1693,7 +1693,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>P003</t>
+          <t>P014</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -1702,10 +1702,10 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>357.1</v>
+        <v>2194.07</v>
       </c>
       <c r="F38" t="n">
-        <v>357.1</v>
+        <v>2194.07</v>
       </c>
       <c r="G38" t="n">
         <v>0</v>
@@ -1727,7 +1727,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>P003</t>
+          <t>P014</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -1736,10 +1736,10 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>1019.82</v>
+        <v>1819.46</v>
       </c>
       <c r="F39" t="n">
-        <v>1019.82</v>
+        <v>1819.46</v>
       </c>
       <c r="G39" t="n">
         <v>0</v>
@@ -1761,7 +1761,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>P003</t>
+          <t>P014</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -1770,10 +1770,10 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>903.45</v>
+        <v>1721.47</v>
       </c>
       <c r="F40" t="n">
-        <v>903.45</v>
+        <v>1721.47</v>
       </c>
       <c r="G40" t="n">
         <v>0</v>
@@ -1795,7 +1795,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>P003</t>
+          <t>P014</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -1804,10 +1804,10 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>612.16</v>
+        <v>1604.07</v>
       </c>
       <c r="F41" t="n">
-        <v>612.16</v>
+        <v>1604.07</v>
       </c>
       <c r="G41" t="n">
         <v>0</v>
@@ -1829,7 +1829,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>P003</t>
+          <t>P014</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -1838,10 +1838,10 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>0</v>
+        <v>2132.06</v>
       </c>
       <c r="F42" t="n">
-        <v>0</v>
+        <v>2132.06</v>
       </c>
       <c r="G42" t="n">
         <v>0</v>
@@ -1863,7 +1863,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>P003</t>
+          <t>P014</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -1872,10 +1872,10 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>536.41</v>
+        <v>1357.66</v>
       </c>
       <c r="F43" t="n">
-        <v>536.41</v>
+        <v>1357.66</v>
       </c>
       <c r="G43" t="n">
         <v>0</v>
@@ -1897,7 +1897,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>P018</t>
+          <t>P020</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -1906,10 +1906,10 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6951.43</v>
+        <v>10804.84</v>
       </c>
       <c r="F44" t="n">
-        <v>6951.43</v>
+        <v>10804.84</v>
       </c>
       <c r="G44" t="n">
         <v>0</v>
@@ -1931,7 +1931,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>P018</t>
+          <t>P020</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -1940,10 +1940,10 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6052.65</v>
+        <v>11757.24</v>
       </c>
       <c r="F45" t="n">
-        <v>6052.65</v>
+        <v>11757.24</v>
       </c>
       <c r="G45" t="n">
         <v>0</v>
@@ -1965,7 +1965,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>P018</t>
+          <t>P020</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -1974,10 +1974,10 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6086.8</v>
+        <v>11926.06</v>
       </c>
       <c r="F46" t="n">
-        <v>6086.8</v>
+        <v>11926.06</v>
       </c>
       <c r="G46" t="n">
         <v>0</v>
@@ -1999,7 +1999,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>P018</t>
+          <t>P020</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -2008,10 +2008,10 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6006.21</v>
+        <v>11614.43</v>
       </c>
       <c r="F47" t="n">
-        <v>6006.21</v>
+        <v>11614.43</v>
       </c>
       <c r="G47" t="n">
         <v>0</v>
@@ -2033,7 +2033,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>P018</t>
+          <t>P020</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -2042,10 +2042,10 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6781.73</v>
+        <v>10964.43</v>
       </c>
       <c r="F48" t="n">
-        <v>6781.73</v>
+        <v>10964.43</v>
       </c>
       <c r="G48" t="n">
         <v>0</v>
@@ -2067,7 +2067,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>P018</t>
+          <t>P020</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -2076,10 +2076,10 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6951.73</v>
+        <v>10064.8</v>
       </c>
       <c r="F49" t="n">
-        <v>6951.73</v>
+        <v>10064.8</v>
       </c>
       <c r="G49" t="n">
         <v>0</v>
@@ -2101,7 +2101,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>P018</t>
+          <t>P020</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -2110,10 +2110,10 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6176.67</v>
+        <v>10241.9</v>
       </c>
       <c r="F50" t="n">
-        <v>6176.67</v>
+        <v>10241.9</v>
       </c>
       <c r="G50" t="n">
         <v>0</v>
@@ -2135,7 +2135,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>P007</t>
+          <t>P017</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -2144,10 +2144,10 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>969.24</v>
+        <v>1022</v>
       </c>
       <c r="F51" t="n">
-        <v>969.24</v>
+        <v>1022</v>
       </c>
       <c r="G51" t="n">
         <v>0</v>
@@ -2169,7 +2169,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>P007</t>
+          <t>P017</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -2178,10 +2178,10 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>745.65</v>
+        <v>904.08</v>
       </c>
       <c r="F52" t="n">
-        <v>745.65</v>
+        <v>904.08</v>
       </c>
       <c r="G52" t="n">
         <v>0</v>
@@ -2203,7 +2203,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>P007</t>
+          <t>P017</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -2212,10 +2212,10 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>1191.6</v>
+        <v>1370</v>
       </c>
       <c r="F53" t="n">
-        <v>1191.6</v>
+        <v>1370</v>
       </c>
       <c r="G53" t="n">
         <v>0</v>
@@ -2237,7 +2237,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>P007</t>
+          <t>P017</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -2246,10 +2246,10 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>1179.5</v>
+        <v>1128.81</v>
       </c>
       <c r="F54" t="n">
-        <v>1179.5</v>
+        <v>1128.81</v>
       </c>
       <c r="G54" t="n">
         <v>0</v>
@@ -2271,7 +2271,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>P007</t>
+          <t>P017</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -2280,10 +2280,10 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>1416.2</v>
+        <v>1476.13</v>
       </c>
       <c r="F55" t="n">
-        <v>1416.2</v>
+        <v>1476.13</v>
       </c>
       <c r="G55" t="n">
         <v>0</v>
@@ -2305,7 +2305,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>P007</t>
+          <t>P017</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -2314,10 +2314,10 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>1175.21</v>
+        <v>1409.31</v>
       </c>
       <c r="F56" t="n">
-        <v>1175.21</v>
+        <v>1409.31</v>
       </c>
       <c r="G56" t="n">
         <v>0</v>
@@ -2339,7 +2339,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>P007</t>
+          <t>P017</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -2348,10 +2348,10 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>4355.64</v>
+        <v>1098.67</v>
       </c>
       <c r="F57" t="n">
-        <v>4355.64</v>
+        <v>1098.67</v>
       </c>
       <c r="G57" t="n">
         <v>0</v>
@@ -2373,7 +2373,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>P017</t>
+          <t>P004</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -2382,10 +2382,10 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>4649.91</v>
+        <v>348.43</v>
       </c>
       <c r="F58" t="n">
-        <v>4649.91</v>
+        <v>348.43</v>
       </c>
       <c r="G58" t="n">
         <v>0</v>
@@ -2407,7 +2407,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>P017</t>
+          <t>P004</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -2416,10 +2416,10 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>4709.63</v>
+        <v>0</v>
       </c>
       <c r="F59" t="n">
-        <v>4709.63</v>
+        <v>0</v>
       </c>
       <c r="G59" t="n">
         <v>0</v>
@@ -2441,7 +2441,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>P017</t>
+          <t>P004</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -2450,10 +2450,10 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>5237.85</v>
+        <v>61.7</v>
       </c>
       <c r="F60" t="n">
-        <v>5237.85</v>
+        <v>61.7</v>
       </c>
       <c r="G60" t="n">
         <v>0</v>
@@ -2475,7 +2475,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>P017</t>
+          <t>P004</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -2484,10 +2484,10 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>5109.15</v>
+        <v>182.69</v>
       </c>
       <c r="F61" t="n">
-        <v>5109.15</v>
+        <v>182.69</v>
       </c>
       <c r="G61" t="n">
         <v>0</v>
@@ -2509,7 +2509,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>P017</t>
+          <t>P004</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -2518,10 +2518,10 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>4632.95</v>
+        <v>0</v>
       </c>
       <c r="F62" t="n">
-        <v>4632.95</v>
+        <v>0</v>
       </c>
       <c r="G62" t="n">
         <v>0</v>
@@ -2543,7 +2543,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>P017</t>
+          <t>P004</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -2552,10 +2552,10 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>4595.77</v>
+        <v>0</v>
       </c>
       <c r="F63" t="n">
-        <v>4595.77</v>
+        <v>0</v>
       </c>
       <c r="G63" t="n">
         <v>0</v>
@@ -2577,7 +2577,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>P017</t>
+          <t>P004</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -2586,10 +2586,10 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>4512.13</v>
+        <v>0</v>
       </c>
       <c r="F64" t="n">
-        <v>4512.13</v>
+        <v>0</v>
       </c>
       <c r="G64" t="n">
         <v>0</v>
@@ -2611,7 +2611,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>P009</t>
+          <t>P013</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -2645,7 +2645,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>P009</t>
+          <t>P013</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -2679,7 +2679,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>P009</t>
+          <t>P013</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -2713,7 +2713,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>P009</t>
+          <t>P013</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -2747,7 +2747,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>P009</t>
+          <t>P013</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -2781,7 +2781,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>P009</t>
+          <t>P013</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -2815,7 +2815,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>P009</t>
+          <t>P013</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -2844,12 +2844,12 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>FR0006</t>
+          <t>FR0004</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>P022</t>
+          <t>P003</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -2858,10 +2858,10 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>8084.54</v>
+        <v>0</v>
       </c>
       <c r="F72" t="n">
-        <v>8084.54</v>
+        <v>0</v>
       </c>
       <c r="G72" t="n">
         <v>0</v>
@@ -2878,12 +2878,12 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>FR0006</t>
+          <t>FR0004</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>P022</t>
+          <t>P003</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -2892,10 +2892,10 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>8917.92</v>
+        <v>0</v>
       </c>
       <c r="F73" t="n">
-        <v>8917.92</v>
+        <v>0</v>
       </c>
       <c r="G73" t="n">
         <v>0</v>
@@ -2912,12 +2912,12 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>FR0006</t>
+          <t>FR0004</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>P022</t>
+          <t>P003</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -2926,10 +2926,10 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>8123.23</v>
+        <v>0</v>
       </c>
       <c r="F74" t="n">
-        <v>8123.23</v>
+        <v>0</v>
       </c>
       <c r="G74" t="n">
         <v>0</v>
@@ -2946,12 +2946,12 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>FR0006</t>
+          <t>FR0004</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>P022</t>
+          <t>P003</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -2960,10 +2960,10 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>8804.790000000001</v>
+        <v>0</v>
       </c>
       <c r="F75" t="n">
-        <v>8804.790000000001</v>
+        <v>0</v>
       </c>
       <c r="G75" t="n">
         <v>0</v>
@@ -2980,12 +2980,12 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>FR0006</t>
+          <t>FR0004</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>P022</t>
+          <t>P003</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -2994,10 +2994,10 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>8258.209999999999</v>
+        <v>0</v>
       </c>
       <c r="F76" t="n">
-        <v>8258.209999999999</v>
+        <v>0</v>
       </c>
       <c r="G76" t="n">
         <v>0</v>
@@ -3014,12 +3014,12 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>FR0006</t>
+          <t>FR0004</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>P022</t>
+          <t>P003</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -3028,10 +3028,10 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>8730.879999999999</v>
+        <v>0</v>
       </c>
       <c r="F77" t="n">
-        <v>8730.879999999999</v>
+        <v>0</v>
       </c>
       <c r="G77" t="n">
         <v>0</v>
@@ -3048,12 +3048,12 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>FR0006</t>
+          <t>FR0004</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>P022</t>
+          <t>P003</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -3062,10 +3062,10 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>9415.09</v>
+        <v>0</v>
       </c>
       <c r="F78" t="n">
-        <v>9415.09</v>
+        <v>0</v>
       </c>
       <c r="G78" t="n">
         <v>0</v>
@@ -3082,12 +3082,12 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>FR0006</t>
+          <t>FR0004</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>P026</t>
+          <t>P010</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -3096,10 +3096,10 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>2053.06</v>
+        <v>256.86</v>
       </c>
       <c r="F79" t="n">
-        <v>2053.06</v>
+        <v>256.86</v>
       </c>
       <c r="G79" t="n">
         <v>0</v>
@@ -3116,12 +3116,12 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>FR0006</t>
+          <t>FR0004</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>P026</t>
+          <t>P010</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -3130,10 +3130,10 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>2441.08</v>
+        <v>0</v>
       </c>
       <c r="F80" t="n">
-        <v>2441.08</v>
+        <v>0</v>
       </c>
       <c r="G80" t="n">
         <v>0</v>
@@ -3150,12 +3150,12 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>FR0006</t>
+          <t>FR0004</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>P026</t>
+          <t>P010</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -3164,10 +3164,10 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>1896.91</v>
+        <v>49.36</v>
       </c>
       <c r="F81" t="n">
-        <v>1896.91</v>
+        <v>49.36</v>
       </c>
       <c r="G81" t="n">
         <v>0</v>
@@ -3184,12 +3184,12 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>FR0006</t>
+          <t>FR0004</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>P026</t>
+          <t>P010</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -3198,10 +3198,10 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>1607.91</v>
+        <v>96.43000000000001</v>
       </c>
       <c r="F82" t="n">
-        <v>1607.91</v>
+        <v>96.43000000000001</v>
       </c>
       <c r="G82" t="n">
         <v>0</v>
@@ -3218,12 +3218,12 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>FR0006</t>
+          <t>FR0004</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>P026</t>
+          <t>P010</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -3232,10 +3232,10 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>1728.91</v>
+        <v>72.37</v>
       </c>
       <c r="F83" t="n">
-        <v>1728.91</v>
+        <v>72.37</v>
       </c>
       <c r="G83" t="n">
         <v>0</v>
@@ -3252,12 +3252,12 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>FR0006</t>
+          <t>FR0004</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>P026</t>
+          <t>P010</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -3266,10 +3266,10 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>2416.43</v>
+        <v>157.34</v>
       </c>
       <c r="F84" t="n">
-        <v>2416.43</v>
+        <v>157.34</v>
       </c>
       <c r="G84" t="n">
         <v>0</v>
@@ -3286,12 +3286,12 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>FR0006</t>
+          <t>FR0004</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>P026</t>
+          <t>P010</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -3300,10 +3300,10 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>1831.12</v>
+        <v>83.04000000000001</v>
       </c>
       <c r="F85" t="n">
-        <v>1831.12</v>
+        <v>83.04000000000001</v>
       </c>
       <c r="G85" t="n">
         <v>0</v>
@@ -3320,12 +3320,12 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>FR0006</t>
+          <t>FR0004</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>P007</t>
+          <t>P008</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -3334,10 +3334,10 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>2096.95</v>
+        <v>5799.59</v>
       </c>
       <c r="F86" t="n">
-        <v>2096.95</v>
+        <v>5799.59</v>
       </c>
       <c r="G86" t="n">
         <v>0</v>
@@ -3354,12 +3354,12 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>FR0006</t>
+          <t>FR0004</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>P007</t>
+          <t>P008</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -3368,10 +3368,10 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>2166.8</v>
+        <v>5491.9</v>
       </c>
       <c r="F87" t="n">
-        <v>2166.8</v>
+        <v>5491.9</v>
       </c>
       <c r="G87" t="n">
         <v>0</v>
@@ -3388,12 +3388,12 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>FR0006</t>
+          <t>FR0004</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>P007</t>
+          <t>P008</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -3402,10 +3402,10 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>1490.78</v>
+        <v>6036.22</v>
       </c>
       <c r="F88" t="n">
-        <v>1490.78</v>
+        <v>6036.22</v>
       </c>
       <c r="G88" t="n">
         <v>0</v>
@@ -3422,12 +3422,12 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>FR0006</t>
+          <t>FR0004</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>P007</t>
+          <t>P008</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -3436,10 +3436,10 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>1610.39</v>
+        <v>7339.56</v>
       </c>
       <c r="F89" t="n">
-        <v>1610.39</v>
+        <v>7339.56</v>
       </c>
       <c r="G89" t="n">
         <v>0</v>
@@ -3456,12 +3456,12 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>FR0006</t>
+          <t>FR0004</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>P007</t>
+          <t>P008</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -3470,10 +3470,10 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>2089.7</v>
+        <v>6860.55</v>
       </c>
       <c r="F90" t="n">
-        <v>2089.7</v>
+        <v>6860.55</v>
       </c>
       <c r="G90" t="n">
         <v>0</v>
@@ -3490,12 +3490,12 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>FR0006</t>
+          <t>FR0004</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>P007</t>
+          <t>P008</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -3504,10 +3504,10 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>1887.11</v>
+        <v>6642.22</v>
       </c>
       <c r="F91" t="n">
-        <v>1887.11</v>
+        <v>6642.22</v>
       </c>
       <c r="G91" t="n">
         <v>0</v>
@@ -3524,12 +3524,12 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>FR0006</t>
+          <t>FR0004</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>P007</t>
+          <t>P008</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -3538,10 +3538,10 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>2389.81</v>
+        <v>5978.47</v>
       </c>
       <c r="F92" t="n">
-        <v>2389.81</v>
+        <v>5978.47</v>
       </c>
       <c r="G92" t="n">
         <v>0</v>
@@ -3572,10 +3572,10 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>1506.01</v>
+        <v>0</v>
       </c>
       <c r="F93" t="n">
-        <v>1506.01</v>
+        <v>0</v>
       </c>
       <c r="G93" t="n">
         <v>0</v>
@@ -3606,10 +3606,10 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>1265.5</v>
+        <v>0</v>
       </c>
       <c r="F94" t="n">
-        <v>1265.5</v>
+        <v>0</v>
       </c>
       <c r="G94" t="n">
         <v>0</v>
@@ -3640,10 +3640,10 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>1515.52</v>
+        <v>0</v>
       </c>
       <c r="F95" t="n">
-        <v>1515.52</v>
+        <v>0</v>
       </c>
       <c r="G95" t="n">
         <v>0</v>
@@ -3674,10 +3674,10 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>2598.93</v>
+        <v>0</v>
       </c>
       <c r="F96" t="n">
-        <v>2598.93</v>
+        <v>0</v>
       </c>
       <c r="G96" t="n">
         <v>0</v>
@@ -3708,10 +3708,10 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>2137.97</v>
+        <v>0</v>
       </c>
       <c r="F97" t="n">
-        <v>2137.97</v>
+        <v>0</v>
       </c>
       <c r="G97" t="n">
         <v>0</v>
@@ -3742,10 +3742,10 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>2082.62</v>
+        <v>0</v>
       </c>
       <c r="F98" t="n">
-        <v>2082.62</v>
+        <v>0</v>
       </c>
       <c r="G98" t="n">
         <v>0</v>
@@ -3776,10 +3776,10 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>2460.04</v>
+        <v>0</v>
       </c>
       <c r="F99" t="n">
-        <v>2460.04</v>
+        <v>0</v>
       </c>
       <c r="G99" t="n">
         <v>0</v>
@@ -3801,7 +3801,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>P004</t>
+          <t>P011</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -3810,10 +3810,10 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>2619.88</v>
+        <v>5644.2</v>
       </c>
       <c r="F100" t="n">
-        <v>2619.88</v>
+        <v>5644.2</v>
       </c>
       <c r="G100" t="n">
         <v>0</v>
@@ -3835,7 +3835,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>P004</t>
+          <t>P011</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -3844,10 +3844,10 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>2970.85</v>
+        <v>5577.45</v>
       </c>
       <c r="F101" t="n">
-        <v>2970.85</v>
+        <v>5577.45</v>
       </c>
       <c r="G101" t="n">
         <v>0</v>
@@ -3869,7 +3869,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>P004</t>
+          <t>P011</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -3878,10 +3878,10 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>2442.59</v>
+        <v>5037.56</v>
       </c>
       <c r="F102" t="n">
-        <v>2442.59</v>
+        <v>5037.56</v>
       </c>
       <c r="G102" t="n">
         <v>0</v>
@@ -3903,7 +3903,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>P004</t>
+          <t>P011</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -3912,10 +3912,10 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>2980.14</v>
+        <v>5759.41</v>
       </c>
       <c r="F103" t="n">
-        <v>2980.14</v>
+        <v>5759.41</v>
       </c>
       <c r="G103" t="n">
         <v>0</v>
@@ -3937,7 +3937,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>P004</t>
+          <t>P011</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -3946,10 +3946,10 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>2748.09</v>
+        <v>5491.32</v>
       </c>
       <c r="F104" t="n">
-        <v>2748.09</v>
+        <v>5491.32</v>
       </c>
       <c r="G104" t="n">
         <v>0</v>
@@ -3971,7 +3971,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>P004</t>
+          <t>P011</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -3980,10 +3980,10 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>2703.68</v>
+        <v>5145.65</v>
       </c>
       <c r="F105" t="n">
-        <v>2703.68</v>
+        <v>5145.65</v>
       </c>
       <c r="G105" t="n">
         <v>0</v>
@@ -4005,7 +4005,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>P004</t>
+          <t>P011</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -4014,10 +4014,10 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>2465.69</v>
+        <v>5389.21</v>
       </c>
       <c r="F106" t="n">
-        <v>2465.69</v>
+        <v>5389.21</v>
       </c>
       <c r="G106" t="n">
         <v>0</v>
@@ -4039,7 +4039,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>P018</t>
+          <t>P022</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -4048,10 +4048,10 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>5189.94</v>
+        <v>1355.99</v>
       </c>
       <c r="F107" t="n">
-        <v>5189.94</v>
+        <v>1355.99</v>
       </c>
       <c r="G107" t="n">
         <v>0</v>
@@ -4073,7 +4073,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>P018</t>
+          <t>P022</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -4082,10 +4082,10 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>5058.15</v>
+        <v>961.17</v>
       </c>
       <c r="F108" t="n">
-        <v>5058.15</v>
+        <v>961.17</v>
       </c>
       <c r="G108" t="n">
         <v>0</v>
@@ -4107,7 +4107,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>P018</t>
+          <t>P022</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -4116,10 +4116,10 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>4435.01</v>
+        <v>743.86</v>
       </c>
       <c r="F109" t="n">
-        <v>4435.01</v>
+        <v>743.86</v>
       </c>
       <c r="G109" t="n">
         <v>0</v>
@@ -4141,7 +4141,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>P018</t>
+          <t>P022</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -4150,10 +4150,10 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>4742.68</v>
+        <v>1377.92</v>
       </c>
       <c r="F110" t="n">
-        <v>4742.68</v>
+        <v>1377.92</v>
       </c>
       <c r="G110" t="n">
         <v>0</v>
@@ -4175,7 +4175,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>P018</t>
+          <t>P022</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -4184,13 +4184,13 @@
         </is>
       </c>
       <c r="E111" t="n">
-        <v>4468.43</v>
+        <v>750.35</v>
       </c>
       <c r="F111" t="n">
-        <v>8533.76</v>
+        <v>750.35</v>
       </c>
       <c r="G111" t="n">
-        <v>4065.33</v>
+        <v>0</v>
       </c>
       <c r="H111" t="inlineStr">
         <is>
@@ -4209,7 +4209,7 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>P018</t>
+          <t>P022</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -4218,10 +4218,10 @@
         </is>
       </c>
       <c r="E112" t="n">
-        <v>4760.78</v>
+        <v>1291.18</v>
       </c>
       <c r="F112" t="n">
-        <v>4760.78</v>
+        <v>1291.18</v>
       </c>
       <c r="G112" t="n">
         <v>0</v>
@@ -4243,7 +4243,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>P018</t>
+          <t>P022</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -4252,10 +4252,10 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>4533.12</v>
+        <v>1421.53</v>
       </c>
       <c r="F113" t="n">
-        <v>4533.12</v>
+        <v>1421.53</v>
       </c>
       <c r="G113" t="n">
         <v>0</v>
@@ -4277,7 +4277,7 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>P008</t>
+          <t>P004</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -4286,10 +4286,10 @@
         </is>
       </c>
       <c r="E114" t="n">
-        <v>0</v>
+        <v>3936.82</v>
       </c>
       <c r="F114" t="n">
-        <v>0</v>
+        <v>3936.82</v>
       </c>
       <c r="G114" t="n">
         <v>0</v>
@@ -4311,7 +4311,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>P008</t>
+          <t>P004</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -4320,10 +4320,10 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>101.92</v>
+        <v>5005.25</v>
       </c>
       <c r="F115" t="n">
-        <v>101.92</v>
+        <v>5005.25</v>
       </c>
       <c r="G115" t="n">
         <v>0</v>
@@ -4345,7 +4345,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>P008</t>
+          <t>P004</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -4354,10 +4354,10 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>262.76</v>
+        <v>3650.1</v>
       </c>
       <c r="F116" t="n">
-        <v>262.76</v>
+        <v>3650.1</v>
       </c>
       <c r="G116" t="n">
         <v>0</v>
@@ -4379,7 +4379,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>P008</t>
+          <t>P004</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -4388,13 +4388,13 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>0</v>
+        <v>4796.14</v>
       </c>
       <c r="F117" t="n">
-        <v>0</v>
+        <v>11036.33</v>
       </c>
       <c r="G117" t="n">
-        <v>0</v>
+        <v>6240.2</v>
       </c>
       <c r="H117" t="inlineStr">
         <is>
@@ -4413,7 +4413,7 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>P008</t>
+          <t>P004</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -4422,10 +4422,10 @@
         </is>
       </c>
       <c r="E118" t="n">
-        <v>280.18</v>
+        <v>3845.7</v>
       </c>
       <c r="F118" t="n">
-        <v>280.18</v>
+        <v>3845.7</v>
       </c>
       <c r="G118" t="n">
         <v>0</v>
@@ -4447,7 +4447,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>P008</t>
+          <t>P004</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -4456,10 +4456,10 @@
         </is>
       </c>
       <c r="E119" t="n">
-        <v>75.45</v>
+        <v>4623.28</v>
       </c>
       <c r="F119" t="n">
-        <v>75.45</v>
+        <v>4623.28</v>
       </c>
       <c r="G119" t="n">
         <v>0</v>
@@ -4481,7 +4481,7 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>P008</t>
+          <t>P004</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -4490,10 +4490,10 @@
         </is>
       </c>
       <c r="E120" t="n">
-        <v>46.32</v>
+        <v>14221.26</v>
       </c>
       <c r="F120" t="n">
-        <v>46.32</v>
+        <v>14221.26</v>
       </c>
       <c r="G120" t="n">
         <v>0</v>
@@ -4510,7 +4510,7 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>FR0007</t>
+          <t>FR0006</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
@@ -4524,10 +4524,10 @@
         </is>
       </c>
       <c r="E121" t="n">
-        <v>1786.4</v>
+        <v>1431.14</v>
       </c>
       <c r="F121" t="n">
-        <v>1786.4</v>
+        <v>1431.14</v>
       </c>
       <c r="G121" t="n">
         <v>0</v>
@@ -4544,7 +4544,7 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>FR0007</t>
+          <t>FR0006</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
@@ -4558,10 +4558,10 @@
         </is>
       </c>
       <c r="E122" t="n">
-        <v>1224.11</v>
+        <v>1186.76</v>
       </c>
       <c r="F122" t="n">
-        <v>1224.11</v>
+        <v>1186.76</v>
       </c>
       <c r="G122" t="n">
         <v>0</v>
@@ -4578,7 +4578,7 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>FR0007</t>
+          <t>FR0006</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
@@ -4592,10 +4592,10 @@
         </is>
       </c>
       <c r="E123" t="n">
-        <v>2122</v>
+        <v>1104.54</v>
       </c>
       <c r="F123" t="n">
-        <v>2122</v>
+        <v>1104.54</v>
       </c>
       <c r="G123" t="n">
         <v>0</v>
@@ -4612,7 +4612,7 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>FR0007</t>
+          <t>FR0006</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
@@ -4626,10 +4626,10 @@
         </is>
       </c>
       <c r="E124" t="n">
-        <v>1666.42</v>
+        <v>1150.47</v>
       </c>
       <c r="F124" t="n">
-        <v>1666.42</v>
+        <v>1150.47</v>
       </c>
       <c r="G124" t="n">
         <v>0</v>
@@ -4646,7 +4646,7 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>FR0007</t>
+          <t>FR0006</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
@@ -4660,10 +4660,10 @@
         </is>
       </c>
       <c r="E125" t="n">
-        <v>1107.51</v>
+        <v>1949.68</v>
       </c>
       <c r="F125" t="n">
-        <v>1107.51</v>
+        <v>1949.68</v>
       </c>
       <c r="G125" t="n">
         <v>0</v>
@@ -4680,7 +4680,7 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>FR0007</t>
+          <t>FR0006</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
@@ -4694,10 +4694,10 @@
         </is>
       </c>
       <c r="E126" t="n">
-        <v>1116.18</v>
+        <v>1501.63</v>
       </c>
       <c r="F126" t="n">
-        <v>1116.18</v>
+        <v>1501.63</v>
       </c>
       <c r="G126" t="n">
         <v>0</v>
@@ -4714,7 +4714,7 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>FR0007</t>
+          <t>FR0006</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
@@ -4728,10 +4728,10 @@
         </is>
       </c>
       <c r="E127" t="n">
-        <v>1953.89</v>
+        <v>1666.8</v>
       </c>
       <c r="F127" t="n">
-        <v>1953.89</v>
+        <v>1666.8</v>
       </c>
       <c r="G127" t="n">
         <v>0</v>
@@ -4753,7 +4753,7 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>P010</t>
+          <t>P016</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
@@ -4762,10 +4762,10 @@
         </is>
       </c>
       <c r="E128" t="n">
-        <v>4256.21</v>
+        <v>591.1799999999999</v>
       </c>
       <c r="F128" t="n">
-        <v>4256.21</v>
+        <v>591.1799999999999</v>
       </c>
       <c r="G128" t="n">
         <v>0</v>
@@ -4787,7 +4787,7 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>P010</t>
+          <t>P016</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
@@ -4796,10 +4796,10 @@
         </is>
       </c>
       <c r="E129" t="n">
-        <v>4732.38</v>
+        <v>402.63</v>
       </c>
       <c r="F129" t="n">
-        <v>4732.38</v>
+        <v>402.63</v>
       </c>
       <c r="G129" t="n">
         <v>0</v>
@@ -4821,7 +4821,7 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>P010</t>
+          <t>P016</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
@@ -4830,10 +4830,10 @@
         </is>
       </c>
       <c r="E130" t="n">
-        <v>4066.87</v>
+        <v>369.46</v>
       </c>
       <c r="F130" t="n">
-        <v>4066.87</v>
+        <v>369.46</v>
       </c>
       <c r="G130" t="n">
         <v>0</v>
@@ -4855,7 +4855,7 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>P010</t>
+          <t>P016</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
@@ -4864,10 +4864,10 @@
         </is>
       </c>
       <c r="E131" t="n">
-        <v>4197.79</v>
+        <v>765.53</v>
       </c>
       <c r="F131" t="n">
-        <v>4197.79</v>
+        <v>765.53</v>
       </c>
       <c r="G131" t="n">
         <v>0</v>
@@ -4889,7 +4889,7 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>P010</t>
+          <t>P016</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
@@ -4898,10 +4898,10 @@
         </is>
       </c>
       <c r="E132" t="n">
-        <v>3896.43</v>
+        <v>651.39</v>
       </c>
       <c r="F132" t="n">
-        <v>3896.43</v>
+        <v>651.39</v>
       </c>
       <c r="G132" t="n">
         <v>0</v>
@@ -4923,7 +4923,7 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>P010</t>
+          <t>P016</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
@@ -4932,10 +4932,10 @@
         </is>
       </c>
       <c r="E133" t="n">
-        <v>4738.64</v>
+        <v>773.6900000000001</v>
       </c>
       <c r="F133" t="n">
-        <v>4738.64</v>
+        <v>773.6900000000001</v>
       </c>
       <c r="G133" t="n">
         <v>0</v>
@@ -4957,7 +4957,7 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>P010</t>
+          <t>P016</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
@@ -4966,10 +4966,10 @@
         </is>
       </c>
       <c r="E134" t="n">
-        <v>4693.97</v>
+        <v>474.72</v>
       </c>
       <c r="F134" t="n">
-        <v>4693.97</v>
+        <v>474.72</v>
       </c>
       <c r="G134" t="n">
         <v>0</v>
@@ -4991,7 +4991,7 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>P024</t>
+          <t>P004</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
@@ -5000,10 +5000,10 @@
         </is>
       </c>
       <c r="E135" t="n">
-        <v>8540.620000000001</v>
+        <v>6019.24</v>
       </c>
       <c r="F135" t="n">
-        <v>8540.620000000001</v>
+        <v>6019.24</v>
       </c>
       <c r="G135" t="n">
         <v>0</v>
@@ -5025,7 +5025,7 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>P024</t>
+          <t>P004</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
@@ -5034,10 +5034,10 @@
         </is>
       </c>
       <c r="E136" t="n">
-        <v>7458.63</v>
+        <v>5810.27</v>
       </c>
       <c r="F136" t="n">
-        <v>7458.63</v>
+        <v>5810.27</v>
       </c>
       <c r="G136" t="n">
         <v>0</v>
@@ -5059,7 +5059,7 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>P024</t>
+          <t>P004</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
@@ -5068,13 +5068,13 @@
         </is>
       </c>
       <c r="E137" t="n">
-        <v>7118.08</v>
+        <v>13231.41</v>
       </c>
       <c r="F137" t="n">
-        <v>7118.08</v>
+        <v>19040.71</v>
       </c>
       <c r="G137" t="n">
-        <v>0</v>
+        <v>5809.31</v>
       </c>
       <c r="H137" t="inlineStr">
         <is>
@@ -5093,7 +5093,7 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>P024</t>
+          <t>P004</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
@@ -5102,10 +5102,10 @@
         </is>
       </c>
       <c r="E138" t="n">
-        <v>7906.55</v>
+        <v>4464.22</v>
       </c>
       <c r="F138" t="n">
-        <v>7906.55</v>
+        <v>4464.22</v>
       </c>
       <c r="G138" t="n">
         <v>0</v>
@@ -5127,7 +5127,7 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>P024</t>
+          <t>P004</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
@@ -5136,10 +5136,10 @@
         </is>
       </c>
       <c r="E139" t="n">
-        <v>8103.55</v>
+        <v>5441.42</v>
       </c>
       <c r="F139" t="n">
-        <v>8103.55</v>
+        <v>5441.42</v>
       </c>
       <c r="G139" t="n">
         <v>0</v>
@@ -5161,7 +5161,7 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>P024</t>
+          <t>P004</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
@@ -5170,10 +5170,10 @@
         </is>
       </c>
       <c r="E140" t="n">
-        <v>8120.44</v>
+        <v>4462.28</v>
       </c>
       <c r="F140" t="n">
-        <v>8120.44</v>
+        <v>4462.28</v>
       </c>
       <c r="G140" t="n">
         <v>0</v>
@@ -5195,7 +5195,7 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>P024</t>
+          <t>P004</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
@@ -5204,10 +5204,10 @@
         </is>
       </c>
       <c r="E141" t="n">
-        <v>7145.74</v>
+        <v>4387.14</v>
       </c>
       <c r="F141" t="n">
-        <v>7145.74</v>
+        <v>4387.14</v>
       </c>
       <c r="G141" t="n">
         <v>0</v>
@@ -5229,7 +5229,7 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>P011</t>
+          <t>P008</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
@@ -5238,10 +5238,10 @@
         </is>
       </c>
       <c r="E142" t="n">
-        <v>0</v>
+        <v>3417.16</v>
       </c>
       <c r="F142" t="n">
-        <v>0</v>
+        <v>3417.16</v>
       </c>
       <c r="G142" t="n">
         <v>0</v>
@@ -5263,7 +5263,7 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>P011</t>
+          <t>P008</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
@@ -5272,10 +5272,10 @@
         </is>
       </c>
       <c r="E143" t="n">
-        <v>0</v>
+        <v>3955.34</v>
       </c>
       <c r="F143" t="n">
-        <v>0</v>
+        <v>3955.34</v>
       </c>
       <c r="G143" t="n">
         <v>0</v>
@@ -5297,7 +5297,7 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>P011</t>
+          <t>P008</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
@@ -5306,10 +5306,10 @@
         </is>
       </c>
       <c r="E144" t="n">
-        <v>0</v>
+        <v>3782.08</v>
       </c>
       <c r="F144" t="n">
-        <v>0</v>
+        <v>3782.08</v>
       </c>
       <c r="G144" t="n">
         <v>0</v>
@@ -5331,7 +5331,7 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>P011</t>
+          <t>P008</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
@@ -5340,10 +5340,10 @@
         </is>
       </c>
       <c r="E145" t="n">
-        <v>0</v>
+        <v>3406.98</v>
       </c>
       <c r="F145" t="n">
-        <v>0</v>
+        <v>3406.98</v>
       </c>
       <c r="G145" t="n">
         <v>0</v>
@@ -5365,7 +5365,7 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>P011</t>
+          <t>P008</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
@@ -5374,10 +5374,10 @@
         </is>
       </c>
       <c r="E146" t="n">
-        <v>0</v>
+        <v>4208.11</v>
       </c>
       <c r="F146" t="n">
-        <v>0</v>
+        <v>4208.11</v>
       </c>
       <c r="G146" t="n">
         <v>0</v>
@@ -5399,7 +5399,7 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>P011</t>
+          <t>P008</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
@@ -5408,10 +5408,10 @@
         </is>
       </c>
       <c r="E147" t="n">
-        <v>0</v>
+        <v>3970.94</v>
       </c>
       <c r="F147" t="n">
-        <v>0</v>
+        <v>3970.94</v>
       </c>
       <c r="G147" t="n">
         <v>0</v>
@@ -5433,7 +5433,7 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>P011</t>
+          <t>P008</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
@@ -5442,10 +5442,10 @@
         </is>
       </c>
       <c r="E148" t="n">
-        <v>0</v>
+        <v>4236.04</v>
       </c>
       <c r="F148" t="n">
-        <v>0</v>
+        <v>4236.04</v>
       </c>
       <c r="G148" t="n">
         <v>0</v>
@@ -5467,7 +5467,7 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>P008</t>
+          <t>P029</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
@@ -5476,10 +5476,10 @@
         </is>
       </c>
       <c r="E149" t="n">
-        <v>701.01</v>
+        <v>2709.91</v>
       </c>
       <c r="F149" t="n">
-        <v>701.01</v>
+        <v>2709.91</v>
       </c>
       <c r="G149" t="n">
         <v>0</v>
@@ -5501,7 +5501,7 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>P008</t>
+          <t>P029</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
@@ -5510,10 +5510,10 @@
         </is>
       </c>
       <c r="E150" t="n">
-        <v>782.71</v>
+        <v>2137.36</v>
       </c>
       <c r="F150" t="n">
-        <v>782.71</v>
+        <v>2137.36</v>
       </c>
       <c r="G150" t="n">
         <v>0</v>
@@ -5535,7 +5535,7 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>P008</t>
+          <t>P029</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
@@ -5544,10 +5544,10 @@
         </is>
       </c>
       <c r="E151" t="n">
-        <v>580.8</v>
+        <v>1905.48</v>
       </c>
       <c r="F151" t="n">
-        <v>580.8</v>
+        <v>1905.48</v>
       </c>
       <c r="G151" t="n">
         <v>0</v>
@@ -5569,7 +5569,7 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>P008</t>
+          <t>P029</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
@@ -5578,10 +5578,10 @@
         </is>
       </c>
       <c r="E152" t="n">
-        <v>742.78</v>
+        <v>1809.34</v>
       </c>
       <c r="F152" t="n">
-        <v>742.78</v>
+        <v>1809.34</v>
       </c>
       <c r="G152" t="n">
         <v>0</v>
@@ -5603,7 +5603,7 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>P008</t>
+          <t>P029</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
@@ -5612,10 +5612,10 @@
         </is>
       </c>
       <c r="E153" t="n">
-        <v>336.55</v>
+        <v>2219.87</v>
       </c>
       <c r="F153" t="n">
-        <v>336.55</v>
+        <v>2219.87</v>
       </c>
       <c r="G153" t="n">
         <v>0</v>
@@ -5637,7 +5637,7 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>P008</t>
+          <t>P029</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
@@ -5646,10 +5646,10 @@
         </is>
       </c>
       <c r="E154" t="n">
-        <v>762.0599999999999</v>
+        <v>2791.57</v>
       </c>
       <c r="F154" t="n">
-        <v>762.0599999999999</v>
+        <v>2791.57</v>
       </c>
       <c r="G154" t="n">
         <v>0</v>
@@ -5671,7 +5671,7 @@
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>P008</t>
+          <t>P029</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
@@ -5680,13 +5680,13 @@
         </is>
       </c>
       <c r="E155" t="n">
-        <v>3483.05</v>
+        <v>2463.35</v>
       </c>
       <c r="F155" t="n">
-        <v>11404.11</v>
+        <v>2463.35</v>
       </c>
       <c r="G155" t="n">
-        <v>7921.05</v>
+        <v>0</v>
       </c>
       <c r="H155" t="inlineStr">
         <is>
@@ -5705,7 +5705,7 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>P027</t>
+          <t>P018</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
@@ -5714,10 +5714,10 @@
         </is>
       </c>
       <c r="E156" t="n">
-        <v>391.71</v>
+        <v>0</v>
       </c>
       <c r="F156" t="n">
-        <v>391.71</v>
+        <v>0</v>
       </c>
       <c r="G156" t="n">
         <v>0</v>
@@ -5739,7 +5739,7 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>P027</t>
+          <t>P018</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
@@ -5748,10 +5748,10 @@
         </is>
       </c>
       <c r="E157" t="n">
-        <v>4229.76</v>
+        <v>0</v>
       </c>
       <c r="F157" t="n">
-        <v>4229.76</v>
+        <v>0</v>
       </c>
       <c r="G157" t="n">
         <v>0</v>
@@ -5773,7 +5773,7 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>P027</t>
+          <t>P018</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
@@ -5782,10 +5782,10 @@
         </is>
       </c>
       <c r="E158" t="n">
-        <v>227.27</v>
+        <v>0</v>
       </c>
       <c r="F158" t="n">
-        <v>227.27</v>
+        <v>0</v>
       </c>
       <c r="G158" t="n">
         <v>0</v>
@@ -5807,7 +5807,7 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>P027</t>
+          <t>P018</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
@@ -5816,13 +5816,13 @@
         </is>
       </c>
       <c r="E159" t="n">
-        <v>305.76</v>
+        <v>0</v>
       </c>
       <c r="F159" t="n">
-        <v>9899.49</v>
+        <v>0</v>
       </c>
       <c r="G159" t="n">
-        <v>9593.73</v>
+        <v>0</v>
       </c>
       <c r="H159" t="inlineStr">
         <is>
@@ -5841,7 +5841,7 @@
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>P027</t>
+          <t>P018</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
@@ -5850,10 +5850,10 @@
         </is>
       </c>
       <c r="E160" t="n">
-        <v>492.81</v>
+        <v>0</v>
       </c>
       <c r="F160" t="n">
-        <v>492.81</v>
+        <v>0</v>
       </c>
       <c r="G160" t="n">
         <v>0</v>
@@ -5875,7 +5875,7 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>P027</t>
+          <t>P018</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
@@ -5884,10 +5884,10 @@
         </is>
       </c>
       <c r="E161" t="n">
-        <v>421.8</v>
+        <v>0</v>
       </c>
       <c r="F161" t="n">
-        <v>421.8</v>
+        <v>0</v>
       </c>
       <c r="G161" t="n">
         <v>0</v>
@@ -5909,7 +5909,7 @@
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>P027</t>
+          <t>P018</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
@@ -5918,10 +5918,10 @@
         </is>
       </c>
       <c r="E162" t="n">
-        <v>62.54</v>
+        <v>0</v>
       </c>
       <c r="F162" t="n">
-        <v>62.54</v>
+        <v>0</v>
       </c>
       <c r="G162" t="n">
         <v>0</v>
@@ -5938,12 +5938,12 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>FR0009</t>
+          <t>FR0008</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>P015</t>
+          <t>P011</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
@@ -5952,10 +5952,10 @@
         </is>
       </c>
       <c r="E163" t="n">
-        <v>0</v>
+        <v>6678.79</v>
       </c>
       <c r="F163" t="n">
-        <v>0</v>
+        <v>6678.79</v>
       </c>
       <c r="G163" t="n">
         <v>0</v>
@@ -5972,12 +5972,12 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>FR0009</t>
+          <t>FR0008</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>P015</t>
+          <t>P011</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
@@ -5986,10 +5986,10 @@
         </is>
       </c>
       <c r="E164" t="n">
-        <v>0</v>
+        <v>5568.65</v>
       </c>
       <c r="F164" t="n">
-        <v>0</v>
+        <v>5568.65</v>
       </c>
       <c r="G164" t="n">
         <v>0</v>
@@ -6006,12 +6006,12 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>FR0009</t>
+          <t>FR0008</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>P015</t>
+          <t>P011</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
@@ -6020,10 +6020,10 @@
         </is>
       </c>
       <c r="E165" t="n">
-        <v>0</v>
+        <v>5872.68</v>
       </c>
       <c r="F165" t="n">
-        <v>0</v>
+        <v>5872.68</v>
       </c>
       <c r="G165" t="n">
         <v>0</v>
@@ -6040,12 +6040,12 @@
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>FR0009</t>
+          <t>FR0008</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>P015</t>
+          <t>P011</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
@@ -6054,13 +6054,13 @@
         </is>
       </c>
       <c r="E166" t="n">
-        <v>0</v>
+        <v>6579.58</v>
       </c>
       <c r="F166" t="n">
-        <v>0</v>
+        <v>15891.04</v>
       </c>
       <c r="G166" t="n">
-        <v>0</v>
+        <v>9311.459999999999</v>
       </c>
       <c r="H166" t="inlineStr">
         <is>
@@ -6074,12 +6074,12 @@
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>FR0009</t>
+          <t>FR0008</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>P015</t>
+          <t>P011</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
@@ -6088,10 +6088,10 @@
         </is>
       </c>
       <c r="E167" t="n">
-        <v>0</v>
+        <v>6232.01</v>
       </c>
       <c r="F167" t="n">
-        <v>0</v>
+        <v>6232.01</v>
       </c>
       <c r="G167" t="n">
         <v>0</v>
@@ -6108,12 +6108,12 @@
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>FR0009</t>
+          <t>FR0008</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>P015</t>
+          <t>P011</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
@@ -6122,10 +6122,10 @@
         </is>
       </c>
       <c r="E168" t="n">
-        <v>0</v>
+        <v>6331.55</v>
       </c>
       <c r="F168" t="n">
-        <v>0</v>
+        <v>6331.55</v>
       </c>
       <c r="G168" t="n">
         <v>0</v>
@@ -6142,12 +6142,12 @@
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>FR0009</t>
+          <t>FR0008</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>P015</t>
+          <t>P011</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
@@ -6156,10 +6156,10 @@
         </is>
       </c>
       <c r="E169" t="n">
-        <v>0</v>
+        <v>5537.92</v>
       </c>
       <c r="F169" t="n">
-        <v>0</v>
+        <v>5537.92</v>
       </c>
       <c r="G169" t="n">
         <v>0</v>
@@ -6176,12 +6176,12 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>FR0009</t>
+          <t>FR0008</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>P002</t>
+          <t>P025</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
@@ -6190,10 +6190,10 @@
         </is>
       </c>
       <c r="E170" t="n">
-        <v>0</v>
+        <v>4960.38</v>
       </c>
       <c r="F170" t="n">
-        <v>0</v>
+        <v>4960.38</v>
       </c>
       <c r="G170" t="n">
         <v>0</v>
@@ -6210,12 +6210,12 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>FR0009</t>
+          <t>FR0008</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>P002</t>
+          <t>P025</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
@@ -6224,10 +6224,10 @@
         </is>
       </c>
       <c r="E171" t="n">
-        <v>0</v>
+        <v>6164.01</v>
       </c>
       <c r="F171" t="n">
-        <v>0</v>
+        <v>6164.01</v>
       </c>
       <c r="G171" t="n">
         <v>0</v>
@@ -6244,12 +6244,12 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>FR0009</t>
+          <t>FR0008</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>P002</t>
+          <t>P025</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
@@ -6258,10 +6258,10 @@
         </is>
       </c>
       <c r="E172" t="n">
-        <v>0</v>
+        <v>5590.82</v>
       </c>
       <c r="F172" t="n">
-        <v>0</v>
+        <v>5590.82</v>
       </c>
       <c r="G172" t="n">
         <v>0</v>
@@ -6278,12 +6278,12 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>FR0009</t>
+          <t>FR0008</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>P002</t>
+          <t>P025</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
@@ -6292,10 +6292,10 @@
         </is>
       </c>
       <c r="E173" t="n">
-        <v>0</v>
+        <v>5666.39</v>
       </c>
       <c r="F173" t="n">
-        <v>0</v>
+        <v>5666.39</v>
       </c>
       <c r="G173" t="n">
         <v>0</v>
@@ -6312,12 +6312,12 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>FR0009</t>
+          <t>FR0008</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>P002</t>
+          <t>P025</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
@@ -6326,10 +6326,10 @@
         </is>
       </c>
       <c r="E174" t="n">
-        <v>0</v>
+        <v>4988.85</v>
       </c>
       <c r="F174" t="n">
-        <v>0</v>
+        <v>4988.85</v>
       </c>
       <c r="G174" t="n">
         <v>0</v>
@@ -6346,12 +6346,12 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>FR0009</t>
+          <t>FR0008</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>P002</t>
+          <t>P025</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
@@ -6360,10 +6360,10 @@
         </is>
       </c>
       <c r="E175" t="n">
-        <v>0</v>
+        <v>5127.04</v>
       </c>
       <c r="F175" t="n">
-        <v>0</v>
+        <v>5127.04</v>
       </c>
       <c r="G175" t="n">
         <v>0</v>
@@ -6380,12 +6380,12 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>FR0009</t>
+          <t>FR0008</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>P002</t>
+          <t>P025</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
@@ -6394,10 +6394,10 @@
         </is>
       </c>
       <c r="E176" t="n">
-        <v>0</v>
+        <v>6491.72</v>
       </c>
       <c r="F176" t="n">
-        <v>0</v>
+        <v>6491.72</v>
       </c>
       <c r="G176" t="n">
         <v>0</v>
@@ -6414,12 +6414,12 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>FR0009</t>
+          <t>FR0008</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>P024</t>
+          <t>P006</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
@@ -6428,10 +6428,10 @@
         </is>
       </c>
       <c r="E177" t="n">
-        <v>3271.25</v>
+        <v>3833.5</v>
       </c>
       <c r="F177" t="n">
-        <v>3271.25</v>
+        <v>3833.5</v>
       </c>
       <c r="G177" t="n">
         <v>0</v>
@@ -6448,12 +6448,12 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>FR0009</t>
+          <t>FR0008</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>P024</t>
+          <t>P006</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
@@ -6462,10 +6462,10 @@
         </is>
       </c>
       <c r="E178" t="n">
-        <v>3426.06</v>
+        <v>3223.85</v>
       </c>
       <c r="F178" t="n">
-        <v>3426.06</v>
+        <v>3223.85</v>
       </c>
       <c r="G178" t="n">
         <v>0</v>
@@ -6482,12 +6482,12 @@
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>FR0009</t>
+          <t>FR0008</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>P024</t>
+          <t>P006</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
@@ -6496,10 +6496,10 @@
         </is>
       </c>
       <c r="E179" t="n">
-        <v>3970.09</v>
+        <v>2373</v>
       </c>
       <c r="F179" t="n">
-        <v>3970.09</v>
+        <v>2373</v>
       </c>
       <c r="G179" t="n">
         <v>0</v>
@@ -6516,12 +6516,12 @@
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>FR0009</t>
+          <t>FR0008</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>P024</t>
+          <t>P006</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
@@ -6530,10 +6530,10 @@
         </is>
       </c>
       <c r="E180" t="n">
-        <v>3398.62</v>
+        <v>2400.83</v>
       </c>
       <c r="F180" t="n">
-        <v>3398.62</v>
+        <v>2400.83</v>
       </c>
       <c r="G180" t="n">
         <v>0</v>
@@ -6550,12 +6550,12 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>FR0009</t>
+          <t>FR0008</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>P024</t>
+          <t>P006</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
@@ -6564,10 +6564,10 @@
         </is>
       </c>
       <c r="E181" t="n">
-        <v>3998.41</v>
+        <v>3543.59</v>
       </c>
       <c r="F181" t="n">
-        <v>3998.41</v>
+        <v>3543.59</v>
       </c>
       <c r="G181" t="n">
         <v>0</v>
@@ -6584,12 +6584,12 @@
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>FR0009</t>
+          <t>FR0008</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>P024</t>
+          <t>P006</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
@@ -6598,10 +6598,10 @@
         </is>
       </c>
       <c r="E182" t="n">
-        <v>2694.2</v>
+        <v>2616.62</v>
       </c>
       <c r="F182" t="n">
-        <v>2694.2</v>
+        <v>2616.62</v>
       </c>
       <c r="G182" t="n">
         <v>0</v>
@@ -6618,12 +6618,12 @@
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>FR0009</t>
+          <t>FR0008</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>P024</t>
+          <t>P006</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
@@ -6632,10 +6632,10 @@
         </is>
       </c>
       <c r="E183" t="n">
-        <v>4164.73</v>
+        <v>2893.69</v>
       </c>
       <c r="F183" t="n">
-        <v>4164.73</v>
+        <v>2893.69</v>
       </c>
       <c r="G183" t="n">
         <v>0</v>
@@ -6652,12 +6652,12 @@
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>FR0009</t>
+          <t>FR0008</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>P028</t>
+          <t>P003</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
@@ -6666,13 +6666,13 @@
         </is>
       </c>
       <c r="E184" t="n">
-        <v>520.99</v>
+        <v>1415.36</v>
       </c>
       <c r="F184" t="n">
-        <v>520.99</v>
+        <v>10242.06</v>
       </c>
       <c r="G184" t="n">
-        <v>0</v>
+        <v>8826.700000000001</v>
       </c>
       <c r="H184" t="inlineStr">
         <is>
@@ -6686,12 +6686,12 @@
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>FR0009</t>
+          <t>FR0008</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>P028</t>
+          <t>P003</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
@@ -6700,10 +6700,10 @@
         </is>
       </c>
       <c r="E185" t="n">
-        <v>349.87</v>
+        <v>1797.93</v>
       </c>
       <c r="F185" t="n">
-        <v>349.87</v>
+        <v>1797.93</v>
       </c>
       <c r="G185" t="n">
         <v>0</v>
@@ -6720,12 +6720,12 @@
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>FR0009</t>
+          <t>FR0008</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>P028</t>
+          <t>P003</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
@@ -6734,10 +6734,10 @@
         </is>
       </c>
       <c r="E186" t="n">
-        <v>409.07</v>
+        <v>1542.83</v>
       </c>
       <c r="F186" t="n">
-        <v>409.07</v>
+        <v>1542.83</v>
       </c>
       <c r="G186" t="n">
         <v>0</v>
@@ -6754,12 +6754,12 @@
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>FR0009</t>
+          <t>FR0008</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>P028</t>
+          <t>P003</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
@@ -6768,10 +6768,10 @@
         </is>
       </c>
       <c r="E187" t="n">
-        <v>498.92</v>
+        <v>1084.44</v>
       </c>
       <c r="F187" t="n">
-        <v>498.92</v>
+        <v>1084.44</v>
       </c>
       <c r="G187" t="n">
         <v>0</v>
@@ -6788,12 +6788,12 @@
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>FR0009</t>
+          <t>FR0008</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>P028</t>
+          <t>P003</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
@@ -6802,10 +6802,10 @@
         </is>
       </c>
       <c r="E188" t="n">
-        <v>79.95999999999999</v>
+        <v>1854.25</v>
       </c>
       <c r="F188" t="n">
-        <v>79.95999999999999</v>
+        <v>1854.25</v>
       </c>
       <c r="G188" t="n">
         <v>0</v>
@@ -6822,12 +6822,12 @@
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>FR0009</t>
+          <t>FR0008</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>P028</t>
+          <t>P003</t>
         </is>
       </c>
       <c r="D189" t="inlineStr">
@@ -6836,10 +6836,10 @@
         </is>
       </c>
       <c r="E189" t="n">
-        <v>0</v>
+        <v>1178.23</v>
       </c>
       <c r="F189" t="n">
-        <v>0</v>
+        <v>1178.23</v>
       </c>
       <c r="G189" t="n">
         <v>0</v>
@@ -6856,12 +6856,12 @@
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>FR0009</t>
+          <t>FR0008</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>P028</t>
+          <t>P003</t>
         </is>
       </c>
       <c r="D190" t="inlineStr">
@@ -6870,13 +6870,13 @@
         </is>
       </c>
       <c r="E190" t="n">
-        <v>0</v>
+        <v>2563.06</v>
       </c>
       <c r="F190" t="n">
-        <v>4570.33</v>
+        <v>2563.06</v>
       </c>
       <c r="G190" t="n">
-        <v>4570.33</v>
+        <v>0</v>
       </c>
       <c r="H190" t="inlineStr">
         <is>
@@ -6895,7 +6895,7 @@
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>P030</t>
+          <t>P001</t>
         </is>
       </c>
       <c r="D191" t="inlineStr">
@@ -6904,10 +6904,10 @@
         </is>
       </c>
       <c r="E191" t="n">
-        <v>3011.22</v>
+        <v>1966.05</v>
       </c>
       <c r="F191" t="n">
-        <v>3011.22</v>
+        <v>1966.05</v>
       </c>
       <c r="G191" t="n">
         <v>0</v>
@@ -6929,7 +6929,7 @@
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>P030</t>
+          <t>P001</t>
         </is>
       </c>
       <c r="D192" t="inlineStr">
@@ -6938,10 +6938,10 @@
         </is>
       </c>
       <c r="E192" t="n">
-        <v>2800.52</v>
+        <v>2320.97</v>
       </c>
       <c r="F192" t="n">
-        <v>2800.52</v>
+        <v>2320.97</v>
       </c>
       <c r="G192" t="n">
         <v>0</v>
@@ -6963,7 +6963,7 @@
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>P030</t>
+          <t>P001</t>
         </is>
       </c>
       <c r="D193" t="inlineStr">
@@ -6972,10 +6972,10 @@
         </is>
       </c>
       <c r="E193" t="n">
-        <v>2635.67</v>
+        <v>2201.13</v>
       </c>
       <c r="F193" t="n">
-        <v>2635.67</v>
+        <v>2201.13</v>
       </c>
       <c r="G193" t="n">
         <v>0</v>
@@ -6997,7 +6997,7 @@
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>P030</t>
+          <t>P001</t>
         </is>
       </c>
       <c r="D194" t="inlineStr">
@@ -7006,10 +7006,10 @@
         </is>
       </c>
       <c r="E194" t="n">
-        <v>2847.3</v>
+        <v>2176.77</v>
       </c>
       <c r="F194" t="n">
-        <v>2847.3</v>
+        <v>2176.77</v>
       </c>
       <c r="G194" t="n">
         <v>0</v>
@@ -7031,7 +7031,7 @@
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>P030</t>
+          <t>P001</t>
         </is>
       </c>
       <c r="D195" t="inlineStr">
@@ -7040,10 +7040,10 @@
         </is>
       </c>
       <c r="E195" t="n">
-        <v>2837.29</v>
+        <v>2134.49</v>
       </c>
       <c r="F195" t="n">
-        <v>2837.29</v>
+        <v>2134.49</v>
       </c>
       <c r="G195" t="n">
         <v>0</v>
@@ -7065,7 +7065,7 @@
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>P030</t>
+          <t>P001</t>
         </is>
       </c>
       <c r="D196" t="inlineStr">
@@ -7074,10 +7074,10 @@
         </is>
       </c>
       <c r="E196" t="n">
-        <v>2677.11</v>
+        <v>1836.33</v>
       </c>
       <c r="F196" t="n">
-        <v>2677.11</v>
+        <v>1836.33</v>
       </c>
       <c r="G196" t="n">
         <v>0</v>
@@ -7099,7 +7099,7 @@
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>P030</t>
+          <t>P001</t>
         </is>
       </c>
       <c r="D197" t="inlineStr">
@@ -7108,15 +7108,2157 @@
         </is>
       </c>
       <c r="E197" t="n">
-        <v>2602.81</v>
+        <v>2567.3</v>
       </c>
       <c r="F197" t="n">
-        <v>2602.81</v>
+        <v>2567.3</v>
       </c>
       <c r="G197" t="n">
         <v>0</v>
       </c>
       <c r="H197" t="inlineStr">
+        <is>
+          <t>Processed</t>
+        </is>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="n">
+        <v>197</v>
+      </c>
+      <c r="B198" t="inlineStr">
+        <is>
+          <t>FR0009</t>
+        </is>
+      </c>
+      <c r="C198" t="inlineStr">
+        <is>
+          <t>P005</t>
+        </is>
+      </c>
+      <c r="D198" t="inlineStr">
+        <is>
+          <t>2026-01-01</t>
+        </is>
+      </c>
+      <c r="E198" t="n">
+        <v>5086.49</v>
+      </c>
+      <c r="F198" t="n">
+        <v>5086.49</v>
+      </c>
+      <c r="G198" t="n">
+        <v>0</v>
+      </c>
+      <c r="H198" t="inlineStr">
+        <is>
+          <t>Processed</t>
+        </is>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="n">
+        <v>198</v>
+      </c>
+      <c r="B199" t="inlineStr">
+        <is>
+          <t>FR0009</t>
+        </is>
+      </c>
+      <c r="C199" t="inlineStr">
+        <is>
+          <t>P005</t>
+        </is>
+      </c>
+      <c r="D199" t="inlineStr">
+        <is>
+          <t>2026-02-01</t>
+        </is>
+      </c>
+      <c r="E199" t="n">
+        <v>4590.38</v>
+      </c>
+      <c r="F199" t="n">
+        <v>4590.38</v>
+      </c>
+      <c r="G199" t="n">
+        <v>0</v>
+      </c>
+      <c r="H199" t="inlineStr">
+        <is>
+          <t>Processed</t>
+        </is>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="n">
+        <v>199</v>
+      </c>
+      <c r="B200" t="inlineStr">
+        <is>
+          <t>FR0009</t>
+        </is>
+      </c>
+      <c r="C200" t="inlineStr">
+        <is>
+          <t>P005</t>
+        </is>
+      </c>
+      <c r="D200" t="inlineStr">
+        <is>
+          <t>2026-03-01</t>
+        </is>
+      </c>
+      <c r="E200" t="n">
+        <v>3987.36</v>
+      </c>
+      <c r="F200" t="n">
+        <v>3987.36</v>
+      </c>
+      <c r="G200" t="n">
+        <v>0</v>
+      </c>
+      <c r="H200" t="inlineStr">
+        <is>
+          <t>Processed</t>
+        </is>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="n">
+        <v>200</v>
+      </c>
+      <c r="B201" t="inlineStr">
+        <is>
+          <t>FR0009</t>
+        </is>
+      </c>
+      <c r="C201" t="inlineStr">
+        <is>
+          <t>P005</t>
+        </is>
+      </c>
+      <c r="D201" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="E201" t="n">
+        <v>4642.81</v>
+      </c>
+      <c r="F201" t="n">
+        <v>4642.81</v>
+      </c>
+      <c r="G201" t="n">
+        <v>0</v>
+      </c>
+      <c r="H201" t="inlineStr">
+        <is>
+          <t>Processed</t>
+        </is>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="n">
+        <v>201</v>
+      </c>
+      <c r="B202" t="inlineStr">
+        <is>
+          <t>FR0009</t>
+        </is>
+      </c>
+      <c r="C202" t="inlineStr">
+        <is>
+          <t>P005</t>
+        </is>
+      </c>
+      <c r="D202" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="E202" t="n">
+        <v>4517.46</v>
+      </c>
+      <c r="F202" t="n">
+        <v>4517.46</v>
+      </c>
+      <c r="G202" t="n">
+        <v>0</v>
+      </c>
+      <c r="H202" t="inlineStr">
+        <is>
+          <t>Processed</t>
+        </is>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="n">
+        <v>202</v>
+      </c>
+      <c r="B203" t="inlineStr">
+        <is>
+          <t>FR0009</t>
+        </is>
+      </c>
+      <c r="C203" t="inlineStr">
+        <is>
+          <t>P005</t>
+        </is>
+      </c>
+      <c r="D203" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="E203" t="n">
+        <v>4745.61</v>
+      </c>
+      <c r="F203" t="n">
+        <v>4745.61</v>
+      </c>
+      <c r="G203" t="n">
+        <v>0</v>
+      </c>
+      <c r="H203" t="inlineStr">
+        <is>
+          <t>Processed</t>
+        </is>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="n">
+        <v>203</v>
+      </c>
+      <c r="B204" t="inlineStr">
+        <is>
+          <t>FR0009</t>
+        </is>
+      </c>
+      <c r="C204" t="inlineStr">
+        <is>
+          <t>P005</t>
+        </is>
+      </c>
+      <c r="D204" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="E204" t="n">
+        <v>4630.24</v>
+      </c>
+      <c r="F204" t="n">
+        <v>4630.24</v>
+      </c>
+      <c r="G204" t="n">
+        <v>0</v>
+      </c>
+      <c r="H204" t="inlineStr">
+        <is>
+          <t>Processed</t>
+        </is>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="n">
+        <v>204</v>
+      </c>
+      <c r="B205" t="inlineStr">
+        <is>
+          <t>FR0009</t>
+        </is>
+      </c>
+      <c r="C205" t="inlineStr">
+        <is>
+          <t>P028</t>
+        </is>
+      </c>
+      <c r="D205" t="inlineStr">
+        <is>
+          <t>2026-01-01</t>
+        </is>
+      </c>
+      <c r="E205" t="n">
+        <v>0</v>
+      </c>
+      <c r="F205" t="n">
+        <v>0</v>
+      </c>
+      <c r="G205" t="n">
+        <v>0</v>
+      </c>
+      <c r="H205" t="inlineStr">
+        <is>
+          <t>Processed</t>
+        </is>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="n">
+        <v>205</v>
+      </c>
+      <c r="B206" t="inlineStr">
+        <is>
+          <t>FR0009</t>
+        </is>
+      </c>
+      <c r="C206" t="inlineStr">
+        <is>
+          <t>P028</t>
+        </is>
+      </c>
+      <c r="D206" t="inlineStr">
+        <is>
+          <t>2026-02-01</t>
+        </is>
+      </c>
+      <c r="E206" t="n">
+        <v>0</v>
+      </c>
+      <c r="F206" t="n">
+        <v>0</v>
+      </c>
+      <c r="G206" t="n">
+        <v>0</v>
+      </c>
+      <c r="H206" t="inlineStr">
+        <is>
+          <t>Processed</t>
+        </is>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="n">
+        <v>206</v>
+      </c>
+      <c r="B207" t="inlineStr">
+        <is>
+          <t>FR0009</t>
+        </is>
+      </c>
+      <c r="C207" t="inlineStr">
+        <is>
+          <t>P028</t>
+        </is>
+      </c>
+      <c r="D207" t="inlineStr">
+        <is>
+          <t>2026-03-01</t>
+        </is>
+      </c>
+      <c r="E207" t="n">
+        <v>0</v>
+      </c>
+      <c r="F207" t="n">
+        <v>0</v>
+      </c>
+      <c r="G207" t="n">
+        <v>0</v>
+      </c>
+      <c r="H207" t="inlineStr">
+        <is>
+          <t>Processed</t>
+        </is>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="n">
+        <v>207</v>
+      </c>
+      <c r="B208" t="inlineStr">
+        <is>
+          <t>FR0009</t>
+        </is>
+      </c>
+      <c r="C208" t="inlineStr">
+        <is>
+          <t>P028</t>
+        </is>
+      </c>
+      <c r="D208" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="E208" t="n">
+        <v>0</v>
+      </c>
+      <c r="F208" t="n">
+        <v>0</v>
+      </c>
+      <c r="G208" t="n">
+        <v>0</v>
+      </c>
+      <c r="H208" t="inlineStr">
+        <is>
+          <t>Processed</t>
+        </is>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="n">
+        <v>208</v>
+      </c>
+      <c r="B209" t="inlineStr">
+        <is>
+          <t>FR0009</t>
+        </is>
+      </c>
+      <c r="C209" t="inlineStr">
+        <is>
+          <t>P028</t>
+        </is>
+      </c>
+      <c r="D209" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="E209" t="n">
+        <v>0</v>
+      </c>
+      <c r="F209" t="n">
+        <v>0</v>
+      </c>
+      <c r="G209" t="n">
+        <v>0</v>
+      </c>
+      <c r="H209" t="inlineStr">
+        <is>
+          <t>Processed</t>
+        </is>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="n">
+        <v>209</v>
+      </c>
+      <c r="B210" t="inlineStr">
+        <is>
+          <t>FR0009</t>
+        </is>
+      </c>
+      <c r="C210" t="inlineStr">
+        <is>
+          <t>P028</t>
+        </is>
+      </c>
+      <c r="D210" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="E210" t="n">
+        <v>0</v>
+      </c>
+      <c r="F210" t="n">
+        <v>0</v>
+      </c>
+      <c r="G210" t="n">
+        <v>0</v>
+      </c>
+      <c r="H210" t="inlineStr">
+        <is>
+          <t>Processed</t>
+        </is>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="n">
+        <v>210</v>
+      </c>
+      <c r="B211" t="inlineStr">
+        <is>
+          <t>FR0009</t>
+        </is>
+      </c>
+      <c r="C211" t="inlineStr">
+        <is>
+          <t>P028</t>
+        </is>
+      </c>
+      <c r="D211" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="E211" t="n">
+        <v>0</v>
+      </c>
+      <c r="F211" t="n">
+        <v>0</v>
+      </c>
+      <c r="G211" t="n">
+        <v>0</v>
+      </c>
+      <c r="H211" t="inlineStr">
+        <is>
+          <t>Processed</t>
+        </is>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="n">
+        <v>211</v>
+      </c>
+      <c r="B212" t="inlineStr">
+        <is>
+          <t>FR0009</t>
+        </is>
+      </c>
+      <c r="C212" t="inlineStr">
+        <is>
+          <t>P020</t>
+        </is>
+      </c>
+      <c r="D212" t="inlineStr">
+        <is>
+          <t>2026-01-01</t>
+        </is>
+      </c>
+      <c r="E212" t="n">
+        <v>8923.42</v>
+      </c>
+      <c r="F212" t="n">
+        <v>8923.42</v>
+      </c>
+      <c r="G212" t="n">
+        <v>0</v>
+      </c>
+      <c r="H212" t="inlineStr">
+        <is>
+          <t>Processed</t>
+        </is>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="n">
+        <v>212</v>
+      </c>
+      <c r="B213" t="inlineStr">
+        <is>
+          <t>FR0009</t>
+        </is>
+      </c>
+      <c r="C213" t="inlineStr">
+        <is>
+          <t>P020</t>
+        </is>
+      </c>
+      <c r="D213" t="inlineStr">
+        <is>
+          <t>2026-02-01</t>
+        </is>
+      </c>
+      <c r="E213" t="n">
+        <v>9212.379999999999</v>
+      </c>
+      <c r="F213" t="n">
+        <v>9212.379999999999</v>
+      </c>
+      <c r="G213" t="n">
+        <v>0</v>
+      </c>
+      <c r="H213" t="inlineStr">
+        <is>
+          <t>Processed</t>
+        </is>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="n">
+        <v>213</v>
+      </c>
+      <c r="B214" t="inlineStr">
+        <is>
+          <t>FR0009</t>
+        </is>
+      </c>
+      <c r="C214" t="inlineStr">
+        <is>
+          <t>P020</t>
+        </is>
+      </c>
+      <c r="D214" t="inlineStr">
+        <is>
+          <t>2026-03-01</t>
+        </is>
+      </c>
+      <c r="E214" t="n">
+        <v>9530.84</v>
+      </c>
+      <c r="F214" t="n">
+        <v>9530.84</v>
+      </c>
+      <c r="G214" t="n">
+        <v>0</v>
+      </c>
+      <c r="H214" t="inlineStr">
+        <is>
+          <t>Processed</t>
+        </is>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="n">
+        <v>214</v>
+      </c>
+      <c r="B215" t="inlineStr">
+        <is>
+          <t>FR0009</t>
+        </is>
+      </c>
+      <c r="C215" t="inlineStr">
+        <is>
+          <t>P020</t>
+        </is>
+      </c>
+      <c r="D215" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="E215" t="n">
+        <v>10260.04</v>
+      </c>
+      <c r="F215" t="n">
+        <v>10260.04</v>
+      </c>
+      <c r="G215" t="n">
+        <v>0</v>
+      </c>
+      <c r="H215" t="inlineStr">
+        <is>
+          <t>Processed</t>
+        </is>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="n">
+        <v>215</v>
+      </c>
+      <c r="B216" t="inlineStr">
+        <is>
+          <t>FR0009</t>
+        </is>
+      </c>
+      <c r="C216" t="inlineStr">
+        <is>
+          <t>P020</t>
+        </is>
+      </c>
+      <c r="D216" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="E216" t="n">
+        <v>8837.360000000001</v>
+      </c>
+      <c r="F216" t="n">
+        <v>8837.360000000001</v>
+      </c>
+      <c r="G216" t="n">
+        <v>0</v>
+      </c>
+      <c r="H216" t="inlineStr">
+        <is>
+          <t>Processed</t>
+        </is>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="n">
+        <v>216</v>
+      </c>
+      <c r="B217" t="inlineStr">
+        <is>
+          <t>FR0009</t>
+        </is>
+      </c>
+      <c r="C217" t="inlineStr">
+        <is>
+          <t>P020</t>
+        </is>
+      </c>
+      <c r="D217" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="E217" t="n">
+        <v>8753.85</v>
+      </c>
+      <c r="F217" t="n">
+        <v>8753.85</v>
+      </c>
+      <c r="G217" t="n">
+        <v>0</v>
+      </c>
+      <c r="H217" t="inlineStr">
+        <is>
+          <t>Processed</t>
+        </is>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" t="n">
+        <v>217</v>
+      </c>
+      <c r="B218" t="inlineStr">
+        <is>
+          <t>FR0009</t>
+        </is>
+      </c>
+      <c r="C218" t="inlineStr">
+        <is>
+          <t>P020</t>
+        </is>
+      </c>
+      <c r="D218" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="E218" t="n">
+        <v>9557.879999999999</v>
+      </c>
+      <c r="F218" t="n">
+        <v>9557.879999999999</v>
+      </c>
+      <c r="G218" t="n">
+        <v>0</v>
+      </c>
+      <c r="H218" t="inlineStr">
+        <is>
+          <t>Processed</t>
+        </is>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="n">
+        <v>218</v>
+      </c>
+      <c r="B219" t="inlineStr">
+        <is>
+          <t>FR0010</t>
+        </is>
+      </c>
+      <c r="C219" t="inlineStr">
+        <is>
+          <t>P002</t>
+        </is>
+      </c>
+      <c r="D219" t="inlineStr">
+        <is>
+          <t>2026-01-01</t>
+        </is>
+      </c>
+      <c r="E219" t="n">
+        <v>1309.86</v>
+      </c>
+      <c r="F219" t="n">
+        <v>1309.86</v>
+      </c>
+      <c r="G219" t="n">
+        <v>0</v>
+      </c>
+      <c r="H219" t="inlineStr">
+        <is>
+          <t>Processed</t>
+        </is>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" t="n">
+        <v>219</v>
+      </c>
+      <c r="B220" t="inlineStr">
+        <is>
+          <t>FR0010</t>
+        </is>
+      </c>
+      <c r="C220" t="inlineStr">
+        <is>
+          <t>P002</t>
+        </is>
+      </c>
+      <c r="D220" t="inlineStr">
+        <is>
+          <t>2026-02-01</t>
+        </is>
+      </c>
+      <c r="E220" t="n">
+        <v>1511.02</v>
+      </c>
+      <c r="F220" t="n">
+        <v>1511.02</v>
+      </c>
+      <c r="G220" t="n">
+        <v>0</v>
+      </c>
+      <c r="H220" t="inlineStr">
+        <is>
+          <t>Processed</t>
+        </is>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="n">
+        <v>220</v>
+      </c>
+      <c r="B221" t="inlineStr">
+        <is>
+          <t>FR0010</t>
+        </is>
+      </c>
+      <c r="C221" t="inlineStr">
+        <is>
+          <t>P002</t>
+        </is>
+      </c>
+      <c r="D221" t="inlineStr">
+        <is>
+          <t>2026-03-01</t>
+        </is>
+      </c>
+      <c r="E221" t="n">
+        <v>1268.99</v>
+      </c>
+      <c r="F221" t="n">
+        <v>1268.99</v>
+      </c>
+      <c r="G221" t="n">
+        <v>0</v>
+      </c>
+      <c r="H221" t="inlineStr">
+        <is>
+          <t>Processed</t>
+        </is>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" t="n">
+        <v>221</v>
+      </c>
+      <c r="B222" t="inlineStr">
+        <is>
+          <t>FR0010</t>
+        </is>
+      </c>
+      <c r="C222" t="inlineStr">
+        <is>
+          <t>P002</t>
+        </is>
+      </c>
+      <c r="D222" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="E222" t="n">
+        <v>980.72</v>
+      </c>
+      <c r="F222" t="n">
+        <v>980.72</v>
+      </c>
+      <c r="G222" t="n">
+        <v>0</v>
+      </c>
+      <c r="H222" t="inlineStr">
+        <is>
+          <t>Processed</t>
+        </is>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" t="n">
+        <v>222</v>
+      </c>
+      <c r="B223" t="inlineStr">
+        <is>
+          <t>FR0010</t>
+        </is>
+      </c>
+      <c r="C223" t="inlineStr">
+        <is>
+          <t>P002</t>
+        </is>
+      </c>
+      <c r="D223" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="E223" t="n">
+        <v>1671.7</v>
+      </c>
+      <c r="F223" t="n">
+        <v>1671.7</v>
+      </c>
+      <c r="G223" t="n">
+        <v>0</v>
+      </c>
+      <c r="H223" t="inlineStr">
+        <is>
+          <t>Processed</t>
+        </is>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" t="n">
+        <v>223</v>
+      </c>
+      <c r="B224" t="inlineStr">
+        <is>
+          <t>FR0010</t>
+        </is>
+      </c>
+      <c r="C224" t="inlineStr">
+        <is>
+          <t>P002</t>
+        </is>
+      </c>
+      <c r="D224" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="E224" t="n">
+        <v>1260.59</v>
+      </c>
+      <c r="F224" t="n">
+        <v>1260.59</v>
+      </c>
+      <c r="G224" t="n">
+        <v>0</v>
+      </c>
+      <c r="H224" t="inlineStr">
+        <is>
+          <t>Processed</t>
+        </is>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" t="n">
+        <v>224</v>
+      </c>
+      <c r="B225" t="inlineStr">
+        <is>
+          <t>FR0010</t>
+        </is>
+      </c>
+      <c r="C225" t="inlineStr">
+        <is>
+          <t>P002</t>
+        </is>
+      </c>
+      <c r="D225" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="E225" t="n">
+        <v>1662.9</v>
+      </c>
+      <c r="F225" t="n">
+        <v>1662.9</v>
+      </c>
+      <c r="G225" t="n">
+        <v>0</v>
+      </c>
+      <c r="H225" t="inlineStr">
+        <is>
+          <t>Processed</t>
+        </is>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" t="n">
+        <v>225</v>
+      </c>
+      <c r="B226" t="inlineStr">
+        <is>
+          <t>FR0010</t>
+        </is>
+      </c>
+      <c r="C226" t="inlineStr">
+        <is>
+          <t>P019</t>
+        </is>
+      </c>
+      <c r="D226" t="inlineStr">
+        <is>
+          <t>2026-01-01</t>
+        </is>
+      </c>
+      <c r="E226" t="n">
+        <v>3135.92</v>
+      </c>
+      <c r="F226" t="n">
+        <v>3135.92</v>
+      </c>
+      <c r="G226" t="n">
+        <v>0</v>
+      </c>
+      <c r="H226" t="inlineStr">
+        <is>
+          <t>Processed</t>
+        </is>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" t="n">
+        <v>226</v>
+      </c>
+      <c r="B227" t="inlineStr">
+        <is>
+          <t>FR0010</t>
+        </is>
+      </c>
+      <c r="C227" t="inlineStr">
+        <is>
+          <t>P019</t>
+        </is>
+      </c>
+      <c r="D227" t="inlineStr">
+        <is>
+          <t>2026-02-01</t>
+        </is>
+      </c>
+      <c r="E227" t="n">
+        <v>1611.3</v>
+      </c>
+      <c r="F227" t="n">
+        <v>1611.3</v>
+      </c>
+      <c r="G227" t="n">
+        <v>0</v>
+      </c>
+      <c r="H227" t="inlineStr">
+        <is>
+          <t>Processed</t>
+        </is>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" t="n">
+        <v>227</v>
+      </c>
+      <c r="B228" t="inlineStr">
+        <is>
+          <t>FR0010</t>
+        </is>
+      </c>
+      <c r="C228" t="inlineStr">
+        <is>
+          <t>P019</t>
+        </is>
+      </c>
+      <c r="D228" t="inlineStr">
+        <is>
+          <t>2026-03-01</t>
+        </is>
+      </c>
+      <c r="E228" t="n">
+        <v>1876.21</v>
+      </c>
+      <c r="F228" t="n">
+        <v>1876.21</v>
+      </c>
+      <c r="G228" t="n">
+        <v>0</v>
+      </c>
+      <c r="H228" t="inlineStr">
+        <is>
+          <t>Processed</t>
+        </is>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" t="n">
+        <v>228</v>
+      </c>
+      <c r="B229" t="inlineStr">
+        <is>
+          <t>FR0010</t>
+        </is>
+      </c>
+      <c r="C229" t="inlineStr">
+        <is>
+          <t>P019</t>
+        </is>
+      </c>
+      <c r="D229" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="E229" t="n">
+        <v>1846.71</v>
+      </c>
+      <c r="F229" t="n">
+        <v>6611.41</v>
+      </c>
+      <c r="G229" t="n">
+        <v>4764.71</v>
+      </c>
+      <c r="H229" t="inlineStr">
+        <is>
+          <t>Processed</t>
+        </is>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" t="n">
+        <v>229</v>
+      </c>
+      <c r="B230" t="inlineStr">
+        <is>
+          <t>FR0010</t>
+        </is>
+      </c>
+      <c r="C230" t="inlineStr">
+        <is>
+          <t>P019</t>
+        </is>
+      </c>
+      <c r="D230" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="E230" t="n">
+        <v>3247.74</v>
+      </c>
+      <c r="F230" t="n">
+        <v>3247.74</v>
+      </c>
+      <c r="G230" t="n">
+        <v>0</v>
+      </c>
+      <c r="H230" t="inlineStr">
+        <is>
+          <t>Processed</t>
+        </is>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" t="n">
+        <v>230</v>
+      </c>
+      <c r="B231" t="inlineStr">
+        <is>
+          <t>FR0010</t>
+        </is>
+      </c>
+      <c r="C231" t="inlineStr">
+        <is>
+          <t>P019</t>
+        </is>
+      </c>
+      <c r="D231" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="E231" t="n">
+        <v>2201.25</v>
+      </c>
+      <c r="F231" t="n">
+        <v>2201.25</v>
+      </c>
+      <c r="G231" t="n">
+        <v>0</v>
+      </c>
+      <c r="H231" t="inlineStr">
+        <is>
+          <t>Processed</t>
+        </is>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" t="n">
+        <v>231</v>
+      </c>
+      <c r="B232" t="inlineStr">
+        <is>
+          <t>FR0010</t>
+        </is>
+      </c>
+      <c r="C232" t="inlineStr">
+        <is>
+          <t>P019</t>
+        </is>
+      </c>
+      <c r="D232" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="E232" t="n">
+        <v>2622.29</v>
+      </c>
+      <c r="F232" t="n">
+        <v>2622.29</v>
+      </c>
+      <c r="G232" t="n">
+        <v>0</v>
+      </c>
+      <c r="H232" t="inlineStr">
+        <is>
+          <t>Processed</t>
+        </is>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" t="n">
+        <v>232</v>
+      </c>
+      <c r="B233" t="inlineStr">
+        <is>
+          <t>FR0010</t>
+        </is>
+      </c>
+      <c r="C233" t="inlineStr">
+        <is>
+          <t>P018</t>
+        </is>
+      </c>
+      <c r="D233" t="inlineStr">
+        <is>
+          <t>2026-01-01</t>
+        </is>
+      </c>
+      <c r="E233" t="n">
+        <v>295.22</v>
+      </c>
+      <c r="F233" t="n">
+        <v>295.22</v>
+      </c>
+      <c r="G233" t="n">
+        <v>0</v>
+      </c>
+      <c r="H233" t="inlineStr">
+        <is>
+          <t>Processed</t>
+        </is>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" t="n">
+        <v>233</v>
+      </c>
+      <c r="B234" t="inlineStr">
+        <is>
+          <t>FR0010</t>
+        </is>
+      </c>
+      <c r="C234" t="inlineStr">
+        <is>
+          <t>P018</t>
+        </is>
+      </c>
+      <c r="D234" t="inlineStr">
+        <is>
+          <t>2026-02-01</t>
+        </is>
+      </c>
+      <c r="E234" t="n">
+        <v>0</v>
+      </c>
+      <c r="F234" t="n">
+        <v>0</v>
+      </c>
+      <c r="G234" t="n">
+        <v>0</v>
+      </c>
+      <c r="H234" t="inlineStr">
+        <is>
+          <t>Processed</t>
+        </is>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" t="n">
+        <v>234</v>
+      </c>
+      <c r="B235" t="inlineStr">
+        <is>
+          <t>FR0010</t>
+        </is>
+      </c>
+      <c r="C235" t="inlineStr">
+        <is>
+          <t>P018</t>
+        </is>
+      </c>
+      <c r="D235" t="inlineStr">
+        <is>
+          <t>2026-03-01</t>
+        </is>
+      </c>
+      <c r="E235" t="n">
+        <v>177.05</v>
+      </c>
+      <c r="F235" t="n">
+        <v>177.05</v>
+      </c>
+      <c r="G235" t="n">
+        <v>0</v>
+      </c>
+      <c r="H235" t="inlineStr">
+        <is>
+          <t>Processed</t>
+        </is>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" t="n">
+        <v>235</v>
+      </c>
+      <c r="B236" t="inlineStr">
+        <is>
+          <t>FR0010</t>
+        </is>
+      </c>
+      <c r="C236" t="inlineStr">
+        <is>
+          <t>P018</t>
+        </is>
+      </c>
+      <c r="D236" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="E236" t="n">
+        <v>146.55</v>
+      </c>
+      <c r="F236" t="n">
+        <v>146.55</v>
+      </c>
+      <c r="G236" t="n">
+        <v>0</v>
+      </c>
+      <c r="H236" t="inlineStr">
+        <is>
+          <t>Processed</t>
+        </is>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" t="n">
+        <v>236</v>
+      </c>
+      <c r="B237" t="inlineStr">
+        <is>
+          <t>FR0010</t>
+        </is>
+      </c>
+      <c r="C237" t="inlineStr">
+        <is>
+          <t>P018</t>
+        </is>
+      </c>
+      <c r="D237" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="E237" t="n">
+        <v>313.19</v>
+      </c>
+      <c r="F237" t="n">
+        <v>313.19</v>
+      </c>
+      <c r="G237" t="n">
+        <v>0</v>
+      </c>
+      <c r="H237" t="inlineStr">
+        <is>
+          <t>Processed</t>
+        </is>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" t="n">
+        <v>237</v>
+      </c>
+      <c r="B238" t="inlineStr">
+        <is>
+          <t>FR0010</t>
+        </is>
+      </c>
+      <c r="C238" t="inlineStr">
+        <is>
+          <t>P018</t>
+        </is>
+      </c>
+      <c r="D238" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="E238" t="n">
+        <v>758.5700000000001</v>
+      </c>
+      <c r="F238" t="n">
+        <v>758.5700000000001</v>
+      </c>
+      <c r="G238" t="n">
+        <v>0</v>
+      </c>
+      <c r="H238" t="inlineStr">
+        <is>
+          <t>Processed</t>
+        </is>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" t="n">
+        <v>238</v>
+      </c>
+      <c r="B239" t="inlineStr">
+        <is>
+          <t>FR0010</t>
+        </is>
+      </c>
+      <c r="C239" t="inlineStr">
+        <is>
+          <t>P018</t>
+        </is>
+      </c>
+      <c r="D239" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="E239" t="n">
+        <v>786.85</v>
+      </c>
+      <c r="F239" t="n">
+        <v>786.85</v>
+      </c>
+      <c r="G239" t="n">
+        <v>0</v>
+      </c>
+      <c r="H239" t="inlineStr">
+        <is>
+          <t>Processed</t>
+        </is>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" t="n">
+        <v>239</v>
+      </c>
+      <c r="B240" t="inlineStr">
+        <is>
+          <t>FR0010</t>
+        </is>
+      </c>
+      <c r="C240" t="inlineStr">
+        <is>
+          <t>P007</t>
+        </is>
+      </c>
+      <c r="D240" t="inlineStr">
+        <is>
+          <t>2026-01-01</t>
+        </is>
+      </c>
+      <c r="E240" t="n">
+        <v>5948.97</v>
+      </c>
+      <c r="F240" t="n">
+        <v>5948.97</v>
+      </c>
+      <c r="G240" t="n">
+        <v>0</v>
+      </c>
+      <c r="H240" t="inlineStr">
+        <is>
+          <t>Processed</t>
+        </is>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" t="n">
+        <v>240</v>
+      </c>
+      <c r="B241" t="inlineStr">
+        <is>
+          <t>FR0010</t>
+        </is>
+      </c>
+      <c r="C241" t="inlineStr">
+        <is>
+          <t>P007</t>
+        </is>
+      </c>
+      <c r="D241" t="inlineStr">
+        <is>
+          <t>2026-02-01</t>
+        </is>
+      </c>
+      <c r="E241" t="n">
+        <v>5964.65</v>
+      </c>
+      <c r="F241" t="n">
+        <v>5964.65</v>
+      </c>
+      <c r="G241" t="n">
+        <v>0</v>
+      </c>
+      <c r="H241" t="inlineStr">
+        <is>
+          <t>Processed</t>
+        </is>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" t="n">
+        <v>241</v>
+      </c>
+      <c r="B242" t="inlineStr">
+        <is>
+          <t>FR0010</t>
+        </is>
+      </c>
+      <c r="C242" t="inlineStr">
+        <is>
+          <t>P007</t>
+        </is>
+      </c>
+      <c r="D242" t="inlineStr">
+        <is>
+          <t>2026-03-01</t>
+        </is>
+      </c>
+      <c r="E242" t="n">
+        <v>5854.47</v>
+      </c>
+      <c r="F242" t="n">
+        <v>5854.47</v>
+      </c>
+      <c r="G242" t="n">
+        <v>0</v>
+      </c>
+      <c r="H242" t="inlineStr">
+        <is>
+          <t>Processed</t>
+        </is>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" t="n">
+        <v>242</v>
+      </c>
+      <c r="B243" t="inlineStr">
+        <is>
+          <t>FR0010</t>
+        </is>
+      </c>
+      <c r="C243" t="inlineStr">
+        <is>
+          <t>P007</t>
+        </is>
+      </c>
+      <c r="D243" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="E243" t="n">
+        <v>6944.92</v>
+      </c>
+      <c r="F243" t="n">
+        <v>6944.92</v>
+      </c>
+      <c r="G243" t="n">
+        <v>0</v>
+      </c>
+      <c r="H243" t="inlineStr">
+        <is>
+          <t>Processed</t>
+        </is>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" t="n">
+        <v>243</v>
+      </c>
+      <c r="B244" t="inlineStr">
+        <is>
+          <t>FR0010</t>
+        </is>
+      </c>
+      <c r="C244" t="inlineStr">
+        <is>
+          <t>P007</t>
+        </is>
+      </c>
+      <c r="D244" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="E244" t="n">
+        <v>6165.98</v>
+      </c>
+      <c r="F244" t="n">
+        <v>6165.98</v>
+      </c>
+      <c r="G244" t="n">
+        <v>0</v>
+      </c>
+      <c r="H244" t="inlineStr">
+        <is>
+          <t>Processed</t>
+        </is>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" t="n">
+        <v>244</v>
+      </c>
+      <c r="B245" t="inlineStr">
+        <is>
+          <t>FR0010</t>
+        </is>
+      </c>
+      <c r="C245" t="inlineStr">
+        <is>
+          <t>P007</t>
+        </is>
+      </c>
+      <c r="D245" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="E245" t="n">
+        <v>6116.25</v>
+      </c>
+      <c r="F245" t="n">
+        <v>6116.25</v>
+      </c>
+      <c r="G245" t="n">
+        <v>0</v>
+      </c>
+      <c r="H245" t="inlineStr">
+        <is>
+          <t>Processed</t>
+        </is>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" t="n">
+        <v>245</v>
+      </c>
+      <c r="B246" t="inlineStr">
+        <is>
+          <t>FR0010</t>
+        </is>
+      </c>
+      <c r="C246" t="inlineStr">
+        <is>
+          <t>P007</t>
+        </is>
+      </c>
+      <c r="D246" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="E246" t="n">
+        <v>6858.09</v>
+      </c>
+      <c r="F246" t="n">
+        <v>6858.09</v>
+      </c>
+      <c r="G246" t="n">
+        <v>0</v>
+      </c>
+      <c r="H246" t="inlineStr">
+        <is>
+          <t>Processed</t>
+        </is>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" t="n">
+        <v>246</v>
+      </c>
+      <c r="B247" t="inlineStr">
+        <is>
+          <t>FR0010</t>
+        </is>
+      </c>
+      <c r="C247" t="inlineStr">
+        <is>
+          <t>P012</t>
+        </is>
+      </c>
+      <c r="D247" t="inlineStr">
+        <is>
+          <t>2026-01-01</t>
+        </is>
+      </c>
+      <c r="E247" t="n">
+        <v>467.46</v>
+      </c>
+      <c r="F247" t="n">
+        <v>467.46</v>
+      </c>
+      <c r="G247" t="n">
+        <v>0</v>
+      </c>
+      <c r="H247" t="inlineStr">
+        <is>
+          <t>Processed</t>
+        </is>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" t="n">
+        <v>247</v>
+      </c>
+      <c r="B248" t="inlineStr">
+        <is>
+          <t>FR0010</t>
+        </is>
+      </c>
+      <c r="C248" t="inlineStr">
+        <is>
+          <t>P012</t>
+        </is>
+      </c>
+      <c r="D248" t="inlineStr">
+        <is>
+          <t>2026-02-01</t>
+        </is>
+      </c>
+      <c r="E248" t="n">
+        <v>504.32</v>
+      </c>
+      <c r="F248" t="n">
+        <v>504.32</v>
+      </c>
+      <c r="G248" t="n">
+        <v>0</v>
+      </c>
+      <c r="H248" t="inlineStr">
+        <is>
+          <t>Processed</t>
+        </is>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" t="n">
+        <v>248</v>
+      </c>
+      <c r="B249" t="inlineStr">
+        <is>
+          <t>FR0010</t>
+        </is>
+      </c>
+      <c r="C249" t="inlineStr">
+        <is>
+          <t>P012</t>
+        </is>
+      </c>
+      <c r="D249" t="inlineStr">
+        <is>
+          <t>2026-03-01</t>
+        </is>
+      </c>
+      <c r="E249" t="n">
+        <v>340.31</v>
+      </c>
+      <c r="F249" t="n">
+        <v>340.31</v>
+      </c>
+      <c r="G249" t="n">
+        <v>0</v>
+      </c>
+      <c r="H249" t="inlineStr">
+        <is>
+          <t>Processed</t>
+        </is>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" t="n">
+        <v>249</v>
+      </c>
+      <c r="B250" t="inlineStr">
+        <is>
+          <t>FR0010</t>
+        </is>
+      </c>
+      <c r="C250" t="inlineStr">
+        <is>
+          <t>P012</t>
+        </is>
+      </c>
+      <c r="D250" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="E250" t="n">
+        <v>910</v>
+      </c>
+      <c r="F250" t="n">
+        <v>910</v>
+      </c>
+      <c r="G250" t="n">
+        <v>0</v>
+      </c>
+      <c r="H250" t="inlineStr">
+        <is>
+          <t>Processed</t>
+        </is>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" t="n">
+        <v>250</v>
+      </c>
+      <c r="B251" t="inlineStr">
+        <is>
+          <t>FR0010</t>
+        </is>
+      </c>
+      <c r="C251" t="inlineStr">
+        <is>
+          <t>P012</t>
+        </is>
+      </c>
+      <c r="D251" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="E251" t="n">
+        <v>448.86</v>
+      </c>
+      <c r="F251" t="n">
+        <v>448.86</v>
+      </c>
+      <c r="G251" t="n">
+        <v>0</v>
+      </c>
+      <c r="H251" t="inlineStr">
+        <is>
+          <t>Processed</t>
+        </is>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" t="n">
+        <v>251</v>
+      </c>
+      <c r="B252" t="inlineStr">
+        <is>
+          <t>FR0010</t>
+        </is>
+      </c>
+      <c r="C252" t="inlineStr">
+        <is>
+          <t>P012</t>
+        </is>
+      </c>
+      <c r="D252" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="E252" t="n">
+        <v>553.34</v>
+      </c>
+      <c r="F252" t="n">
+        <v>553.34</v>
+      </c>
+      <c r="G252" t="n">
+        <v>0</v>
+      </c>
+      <c r="H252" t="inlineStr">
+        <is>
+          <t>Processed</t>
+        </is>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" t="n">
+        <v>252</v>
+      </c>
+      <c r="B253" t="inlineStr">
+        <is>
+          <t>FR0010</t>
+        </is>
+      </c>
+      <c r="C253" t="inlineStr">
+        <is>
+          <t>P012</t>
+        </is>
+      </c>
+      <c r="D253" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="E253" t="n">
+        <v>705.3</v>
+      </c>
+      <c r="F253" t="n">
+        <v>705.3</v>
+      </c>
+      <c r="G253" t="n">
+        <v>0</v>
+      </c>
+      <c r="H253" t="inlineStr">
+        <is>
+          <t>Processed</t>
+        </is>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" t="n">
+        <v>253</v>
+      </c>
+      <c r="B254" t="inlineStr">
+        <is>
+          <t>FR0010</t>
+        </is>
+      </c>
+      <c r="C254" t="inlineStr">
+        <is>
+          <t>P028</t>
+        </is>
+      </c>
+      <c r="D254" t="inlineStr">
+        <is>
+          <t>2026-01-01</t>
+        </is>
+      </c>
+      <c r="E254" t="n">
+        <v>0</v>
+      </c>
+      <c r="F254" t="n">
+        <v>0</v>
+      </c>
+      <c r="G254" t="n">
+        <v>0</v>
+      </c>
+      <c r="H254" t="inlineStr">
+        <is>
+          <t>Processed</t>
+        </is>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" t="n">
+        <v>254</v>
+      </c>
+      <c r="B255" t="inlineStr">
+        <is>
+          <t>FR0010</t>
+        </is>
+      </c>
+      <c r="C255" t="inlineStr">
+        <is>
+          <t>P028</t>
+        </is>
+      </c>
+      <c r="D255" t="inlineStr">
+        <is>
+          <t>2026-02-01</t>
+        </is>
+      </c>
+      <c r="E255" t="n">
+        <v>0</v>
+      </c>
+      <c r="F255" t="n">
+        <v>0</v>
+      </c>
+      <c r="G255" t="n">
+        <v>0</v>
+      </c>
+      <c r="H255" t="inlineStr">
+        <is>
+          <t>Processed</t>
+        </is>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" t="n">
+        <v>255</v>
+      </c>
+      <c r="B256" t="inlineStr">
+        <is>
+          <t>FR0010</t>
+        </is>
+      </c>
+      <c r="C256" t="inlineStr">
+        <is>
+          <t>P028</t>
+        </is>
+      </c>
+      <c r="D256" t="inlineStr">
+        <is>
+          <t>2026-03-01</t>
+        </is>
+      </c>
+      <c r="E256" t="n">
+        <v>0</v>
+      </c>
+      <c r="F256" t="n">
+        <v>0</v>
+      </c>
+      <c r="G256" t="n">
+        <v>0</v>
+      </c>
+      <c r="H256" t="inlineStr">
+        <is>
+          <t>Processed</t>
+        </is>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" t="n">
+        <v>256</v>
+      </c>
+      <c r="B257" t="inlineStr">
+        <is>
+          <t>FR0010</t>
+        </is>
+      </c>
+      <c r="C257" t="inlineStr">
+        <is>
+          <t>P028</t>
+        </is>
+      </c>
+      <c r="D257" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="E257" t="n">
+        <v>0</v>
+      </c>
+      <c r="F257" t="n">
+        <v>0</v>
+      </c>
+      <c r="G257" t="n">
+        <v>0</v>
+      </c>
+      <c r="H257" t="inlineStr">
+        <is>
+          <t>Processed</t>
+        </is>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" t="n">
+        <v>257</v>
+      </c>
+      <c r="B258" t="inlineStr">
+        <is>
+          <t>FR0010</t>
+        </is>
+      </c>
+      <c r="C258" t="inlineStr">
+        <is>
+          <t>P028</t>
+        </is>
+      </c>
+      <c r="D258" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="E258" t="n">
+        <v>2113.59</v>
+      </c>
+      <c r="F258" t="n">
+        <v>2113.59</v>
+      </c>
+      <c r="G258" t="n">
+        <v>0</v>
+      </c>
+      <c r="H258" t="inlineStr">
+        <is>
+          <t>Processed</t>
+        </is>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" t="n">
+        <v>258</v>
+      </c>
+      <c r="B259" t="inlineStr">
+        <is>
+          <t>FR0010</t>
+        </is>
+      </c>
+      <c r="C259" t="inlineStr">
+        <is>
+          <t>P028</t>
+        </is>
+      </c>
+      <c r="D259" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="E259" t="n">
+        <v>0</v>
+      </c>
+      <c r="F259" t="n">
+        <v>0</v>
+      </c>
+      <c r="G259" t="n">
+        <v>0</v>
+      </c>
+      <c r="H259" t="inlineStr">
+        <is>
+          <t>Processed</t>
+        </is>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" t="n">
+        <v>259</v>
+      </c>
+      <c r="B260" t="inlineStr">
+        <is>
+          <t>FR0010</t>
+        </is>
+      </c>
+      <c r="C260" t="inlineStr">
+        <is>
+          <t>P028</t>
+        </is>
+      </c>
+      <c r="D260" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="E260" t="n">
+        <v>0</v>
+      </c>
+      <c r="F260" t="n">
+        <v>0</v>
+      </c>
+      <c r="G260" t="n">
+        <v>0</v>
+      </c>
+      <c r="H260" t="inlineStr">
         <is>
           <t>Processed</t>
         </is>
